--- a/data/sports/kbo/research.xlsx
+++ b/data/sports/kbo/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ162" headerRowCount="1">
-  <autoFilter ref="A1:DQ162"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ167" headerRowCount="1">
+  <autoFilter ref="A1:DQ167"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$162)</f>
+        <f>COUNTA('Picks'!$A$2:$A$167)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$162,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$167,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$162,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$167,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$162,"settled",'Picks'!$V$2:$V$162,"win")+COUNTIFS('Picks'!$U$2:$U$162,"settled",'Picks'!$V$2:$V$162,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"win")+COUNTIFS('Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$162,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$167,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$162,"&gt;0",'Picks'!$V$2:$V$162,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$162,"&gt;0",'Picks'!$V$2:$V$162,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$167,"&gt;0",'Picks'!$V$2:$V$167,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$167,"&gt;0",'Picks'!$V$2:$V$167,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$162,"&gt;0",'Picks'!$V$2:$V$162,"win")/(COUNTIFS('Picks'!$BX$2:$BX$162,"&gt;0",'Picks'!$V$2:$V$162,"win")+COUNTIFS('Picks'!$BX$2:$BX$162,"&gt;0",'Picks'!$V$2:$V$162,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$167,"&gt;0",'Picks'!$V$2:$V$167,"win")/(COUNTIFS('Picks'!$BX$2:$BX$167,"&gt;0",'Picks'!$V$2:$V$167,"win")+COUNTIFS('Picks'!$BX$2:$BX$167,"&gt;0",'Picks'!$V$2:$V$167,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$162)/SUM('Picks'!$BX$2:$BX$162),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$167)/SUM('Picks'!$BX$2:$BX$167),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$162)</f>
+        <f>SUM('Picks'!$BY$2:$BY$167)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$162,"&lt;&gt;",'Picks'!$AB$2:$AB$162),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$167,"&lt;&gt;",'Picks'!$AB$2:$AB$167),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$162,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$162,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$167,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$167,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$162,'Picks'!$AM$2:$AM$162,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$167,'Picks'!$AM$2:$AM$167,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$162,$A14,'Picks'!$U$2:$U$162,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$167,$A14,'Picks'!$U$2:$U$167,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$162,$A14,'Picks'!$U$2:$U$162,"settled",'Picks'!$V$2:$V$162,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$167,$A14,'Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$162,$A14,'Picks'!$U$2:$U$162,"settled",'Picks'!$V$2:$V$162,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$167,$A14,'Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$162,'Picks'!$H$2:$H$162,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$167,'Picks'!$H$2:$H$167,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$162,'Picks'!$H$2:$H$162,$A14,'Picks'!$U$2:$U$162,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$167,'Picks'!$H$2:$H$167,$A14,'Picks'!$U$2:$U$167,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$162,$A15,'Picks'!$U$2:$U$162,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$167,$A15,'Picks'!$U$2:$U$167,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$162,$A15,'Picks'!$U$2:$U$162,"settled",'Picks'!$V$2:$V$162,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$167,$A15,'Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$162,$A15,'Picks'!$U$2:$U$162,"settled",'Picks'!$V$2:$V$162,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$167,$A15,'Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$162,'Picks'!$H$2:$H$162,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$167,'Picks'!$H$2:$H$167,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$162,'Picks'!$H$2:$H$162,$A15,'Picks'!$U$2:$U$162,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$167,'Picks'!$H$2:$H$167,$A15,'Picks'!$U$2:$U$167,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$162,$A16,'Picks'!$U$2:$U$162,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$167,$A16,'Picks'!$U$2:$U$167,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$162,$A16,'Picks'!$U$2:$U$162,"settled",'Picks'!$V$2:$V$162,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$167,$A16,'Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$162,$A16,'Picks'!$U$2:$U$162,"settled",'Picks'!$V$2:$V$162,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$167,$A16,'Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$162,'Picks'!$H$2:$H$162,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$167,'Picks'!$H$2:$H$167,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$162,'Picks'!$H$2:$H$162,$A16,'Picks'!$U$2:$U$162,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$167,'Picks'!$H$2:$H$167,$A16,'Picks'!$U$2:$U$167,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ162"/>
+  <dimension ref="A1:DQ167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -24539,18 +24539,28 @@
       </c>
       <c r="U75" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V75" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V75" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W75" s="26" t="n"/>
       <c r="X75" s="26" t="n"/>
       <c r="Y75" s="25" t="n"/>
       <c r="Z75" s="26" t="n"/>
       <c r="AA75" s="28" t="n"/>
       <c r="AB75" s="28" t="n"/>
-      <c r="AC75" s="30" t="n"/>
-      <c r="AD75" s="24" t="n"/>
+      <c r="AC75" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:58:45.761826Z</t>
+        </is>
+      </c>
       <c r="AE75" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5100 (market_slug=aec-kbo-dbo-khi-2026-08-28). Tie probability=0.0226.</t>
@@ -24699,7 +24709,11 @@
       <c r="BT75" s="28" t="n"/>
       <c r="BU75" s="25" t="n"/>
       <c r="BV75" s="29" t="n"/>
-      <c r="BW75" s="24" t="n"/>
+      <c r="BW75" s="24" t="inlineStr">
+        <is>
+          <t>KBO game scheduled on 2026-08-28 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX75" s="30" t="n"/>
       <c r="BY75" s="27" t="n"/>
       <c r="BZ75" s="24" t="n"/>
@@ -24836,18 +24850,28 @@
       </c>
       <c r="U76" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V76" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V76" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W76" s="26" t="n"/>
       <c r="X76" s="26" t="n"/>
       <c r="Y76" s="25" t="n"/>
       <c r="Z76" s="26" t="n"/>
       <c r="AA76" s="28" t="n"/>
       <c r="AB76" s="28" t="n"/>
-      <c r="AC76" s="30" t="n"/>
-      <c r="AD76" s="24" t="n"/>
+      <c r="AC76" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD76" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:58:50.382279Z</t>
+        </is>
+      </c>
       <c r="AE76" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-kbo-lgo-ltg-2026-08-28). Tie probability=0.0226.</t>
@@ -24996,7 +25020,11 @@
       <c r="BT76" s="28" t="n"/>
       <c r="BU76" s="25" t="n"/>
       <c r="BV76" s="29" t="n"/>
-      <c r="BW76" s="24" t="n"/>
+      <c r="BW76" s="24" t="inlineStr">
+        <is>
+          <t>KBO game scheduled on 2026-08-28 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX76" s="30" t="n"/>
       <c r="BY76" s="27" t="n"/>
       <c r="BZ76" s="24" t="n"/>
@@ -25133,18 +25161,28 @@
       </c>
       <c r="U77" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V77" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V77" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W77" s="26" t="n"/>
       <c r="X77" s="26" t="n"/>
       <c r="Y77" s="25" t="n"/>
       <c r="Z77" s="26" t="n"/>
       <c r="AA77" s="28" t="n"/>
       <c r="AB77" s="28" t="n"/>
-      <c r="AC77" s="30" t="n"/>
-      <c r="AD77" s="24" t="n"/>
+      <c r="AC77" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD77" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:58:55.070528Z</t>
+        </is>
+      </c>
       <c r="AE77" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5100 (market_slug=aec-kbo-sla-kwt-2026-08-28). Tie probability=0.0226.</t>
@@ -25293,7 +25331,11 @@
       <c r="BT77" s="28" t="n"/>
       <c r="BU77" s="25" t="n"/>
       <c r="BV77" s="29" t="n"/>
-      <c r="BW77" s="24" t="n"/>
+      <c r="BW77" s="24" t="inlineStr">
+        <is>
+          <t>KBO game scheduled on 2026-08-28 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX77" s="30" t="n"/>
       <c r="BY77" s="27" t="n"/>
       <c r="BZ77" s="24" t="n"/>
@@ -25430,18 +25472,28 @@
       </c>
       <c r="U78" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V78" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V78" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W78" s="26" t="n"/>
       <c r="X78" s="26" t="n"/>
       <c r="Y78" s="25" t="n"/>
       <c r="Z78" s="26" t="n"/>
       <c r="AA78" s="28" t="n"/>
       <c r="AB78" s="28" t="n"/>
-      <c r="AC78" s="30" t="n"/>
-      <c r="AD78" s="24" t="n"/>
+      <c r="AC78" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD78" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:58:59.778035Z</t>
+        </is>
+      </c>
       <c r="AE78" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6900 (market_slug=aec-kbo-kti-sls-2026-08-28). Tie probability=0.0226.</t>
@@ -25590,7 +25642,11 @@
       <c r="BT78" s="28" t="n"/>
       <c r="BU78" s="25" t="n"/>
       <c r="BV78" s="29" t="n"/>
-      <c r="BW78" s="24" t="n"/>
+      <c r="BW78" s="24" t="inlineStr">
+        <is>
+          <t>KBO game scheduled on 2026-08-28 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX78" s="30" t="n"/>
       <c r="BY78" s="27" t="n"/>
       <c r="BZ78" s="24" t="n"/>
@@ -25727,18 +25783,28 @@
       </c>
       <c r="U79" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V79" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V79" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W79" s="26" t="n"/>
       <c r="X79" s="26" t="n"/>
       <c r="Y79" s="25" t="n"/>
       <c r="Z79" s="26" t="n"/>
       <c r="AA79" s="28" t="n"/>
       <c r="AB79" s="28" t="n"/>
-      <c r="AC79" s="30" t="n"/>
-      <c r="AD79" s="24" t="n"/>
+      <c r="AC79" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD79" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:59:04.543849Z</t>
+        </is>
+      </c>
       <c r="AE79" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4900 (market_slug=aec-kbo-hea-ndc-2026-08-28). Tie probability=0.0226.</t>
@@ -25887,7 +25953,11 @@
       <c r="BT79" s="28" t="n"/>
       <c r="BU79" s="25" t="n"/>
       <c r="BV79" s="29" t="n"/>
-      <c r="BW79" s="24" t="n"/>
+      <c r="BW79" s="24" t="inlineStr">
+        <is>
+          <t>KBO game scheduled on 2026-08-28 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX79" s="30" t="n"/>
       <c r="BY79" s="27" t="n"/>
       <c r="BZ79" s="24" t="n"/>
@@ -26335,18 +26405,28 @@
       </c>
       <c r="U81" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V81" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V81" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W81" s="26" t="n"/>
       <c r="X81" s="26" t="n"/>
       <c r="Y81" s="25" t="n"/>
       <c r="Z81" s="26" t="n"/>
       <c r="AA81" s="28" t="n"/>
       <c r="AB81" s="28" t="n"/>
-      <c r="AC81" s="30" t="n"/>
-      <c r="AD81" s="24" t="n"/>
+      <c r="AC81" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD81" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:59:09.445372Z</t>
+        </is>
+      </c>
       <c r="AE81" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5800 (market_slug=aec-kbo-sla-kwt-2026-08-30). Tie probability=0.0226.</t>
@@ -26495,7 +26575,11 @@
       <c r="BT81" s="28" t="n"/>
       <c r="BU81" s="25" t="n"/>
       <c r="BV81" s="29" t="n"/>
-      <c r="BW81" s="24" t="n"/>
+      <c r="BW81" s="24" t="inlineStr">
+        <is>
+          <t>KBO game scheduled on 2026-08-30 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX81" s="30" t="n"/>
       <c r="BY81" s="27" t="n"/>
       <c r="BZ81" s="24" t="n"/>
@@ -26943,18 +27027,28 @@
       </c>
       <c r="U83" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V83" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V83" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W83" s="26" t="n"/>
       <c r="X83" s="26" t="n"/>
       <c r="Y83" s="25" t="n"/>
       <c r="Z83" s="26" t="n"/>
       <c r="AA83" s="28" t="n"/>
       <c r="AB83" s="28" t="n"/>
-      <c r="AC83" s="30" t="n"/>
-      <c r="AD83" s="24" t="n"/>
+      <c r="AC83" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD83" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:59:14.166627Z</t>
+        </is>
+      </c>
       <c r="AE83" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6600 (market_slug=aec-kbo-kti-sls-2026-08-30). Tie probability=0.0226.</t>
@@ -27103,7 +27197,11 @@
       <c r="BT83" s="28" t="n"/>
       <c r="BU83" s="25" t="n"/>
       <c r="BV83" s="29" t="n"/>
-      <c r="BW83" s="24" t="n"/>
+      <c r="BW83" s="24" t="inlineStr">
+        <is>
+          <t>KBO game scheduled on 2026-08-30 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX83" s="30" t="n"/>
       <c r="BY83" s="27" t="n"/>
       <c r="BZ83" s="24" t="n"/>
@@ -27240,18 +27338,28 @@
       </c>
       <c r="U84" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V84" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V84" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W84" s="26" t="n"/>
       <c r="X84" s="26" t="n"/>
       <c r="Y84" s="25" t="n"/>
       <c r="Z84" s="26" t="n"/>
       <c r="AA84" s="28" t="n"/>
       <c r="AB84" s="28" t="n"/>
-      <c r="AC84" s="30" t="n"/>
-      <c r="AD84" s="24" t="n"/>
+      <c r="AC84" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD84" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:59:18.761476Z</t>
+        </is>
+      </c>
       <c r="AE84" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6300 (market_slug=aec-kbo-lgo-ltg-2026-08-30). Tie probability=0.0226.</t>
@@ -27400,7 +27508,11 @@
       <c r="BT84" s="28" t="n"/>
       <c r="BU84" s="25" t="n"/>
       <c r="BV84" s="29" t="n"/>
-      <c r="BW84" s="24" t="n"/>
+      <c r="BW84" s="24" t="inlineStr">
+        <is>
+          <t>KBO game scheduled on 2026-08-30 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX84" s="30" t="n"/>
       <c r="BY84" s="27" t="n"/>
       <c r="BZ84" s="24" t="n"/>
@@ -37488,18 +37600,28 @@
       </c>
       <c r="U116" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V116" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V116" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W116" s="26" t="n"/>
       <c r="X116" s="26" t="n"/>
       <c r="Y116" s="25" t="n"/>
       <c r="Z116" s="26" t="n"/>
       <c r="AA116" s="28" t="n"/>
       <c r="AB116" s="28" t="n"/>
-      <c r="AC116" s="30" t="n"/>
-      <c r="AD116" s="24" t="n"/>
+      <c r="AC116" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD116" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:59:23.400595Z</t>
+        </is>
+      </c>
       <c r="AE116" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4700 (market_slug=aec-kbo-kti-sla-2026-09-08). Tie probability=0.0225.</t>
@@ -37648,7 +37770,11 @@
       <c r="BT116" s="28" t="n"/>
       <c r="BU116" s="25" t="n"/>
       <c r="BV116" s="29" t="n"/>
-      <c r="BW116" s="24" t="n"/>
+      <c r="BW116" s="24" t="inlineStr">
+        <is>
+          <t>KBO game scheduled on 2026-09-08 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX116" s="30" t="n"/>
       <c r="BY116" s="27" t="n"/>
       <c r="BZ116" s="24" t="n"/>
@@ -45457,18 +45583,28 @@
       </c>
       <c r="U141" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V141" s="24" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V141" s="24" t="inlineStr">
+        <is>
+          <t>push</t>
+        </is>
+      </c>
       <c r="W141" s="26" t="n"/>
       <c r="X141" s="26" t="n"/>
       <c r="Y141" s="25" t="n"/>
       <c r="Z141" s="26" t="n"/>
       <c r="AA141" s="28" t="n"/>
       <c r="AB141" s="28" t="n"/>
-      <c r="AC141" s="30" t="n"/>
-      <c r="AD141" s="24" t="n"/>
+      <c r="AC141" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD141" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:59:28.097374Z</t>
+        </is>
+      </c>
       <c r="AE141" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.3700 (market_slug=aec-kbo-kti-ltg-2026-09-27). Tie probability=0.0226.</t>
@@ -45617,7 +45753,11 @@
       <c r="BT141" s="28" t="n"/>
       <c r="BU141" s="25" t="n"/>
       <c r="BV141" s="29" t="n"/>
-      <c r="BW141" s="24" t="n"/>
+      <c r="BW141" s="24" t="inlineStr">
+        <is>
+          <t>KBO game scheduled on 2026-09-27 cancelled/postponed (no final score posted after &gt;7 days)</t>
+        </is>
+      </c>
       <c r="BX141" s="30" t="n"/>
       <c r="BY141" s="27" t="n"/>
       <c r="BZ141" s="24" t="n"/>
@@ -50796,18 +50936,32 @@
       </c>
       <c r="U158" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V158" s="24" t="n"/>
-      <c r="W158" s="26" t="n"/>
-      <c r="X158" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V158" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W158" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="X158" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y158" s="25" t="n"/>
       <c r="Z158" s="26" t="n"/>
       <c r="AA158" s="28" t="n"/>
       <c r="AB158" s="28" t="n"/>
-      <c r="AC158" s="30" t="n"/>
-      <c r="AD158" s="24" t="n"/>
+      <c r="AC158" s="30" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD158" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:03:38.491687Z</t>
+        </is>
+      </c>
       <c r="AE158" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6000 (market_slug=aec-kbo-ltg-ndc-2026-10-06). Tie probability=0.0226.</t>
@@ -51093,18 +51247,32 @@
       </c>
       <c r="U159" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V159" s="24" t="n"/>
-      <c r="W159" s="26" t="n"/>
-      <c r="X159" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V159" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W159" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X159" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y159" s="25" t="n"/>
       <c r="Z159" s="26" t="n"/>
       <c r="AA159" s="28" t="n"/>
       <c r="AB159" s="28" t="n"/>
-      <c r="AC159" s="30" t="n"/>
-      <c r="AD159" s="24" t="n"/>
+      <c r="AC159" s="30" t="n">
+        <v>0.5881999999999999</v>
+      </c>
+      <c r="AD159" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:03:40.849516Z</t>
+        </is>
+      </c>
       <c r="AE159" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.6300 (market_slug=aec-kbo-lgo-dbo-2026-10-06). Tie probability=0.0226.</t>
@@ -51390,18 +51558,32 @@
       </c>
       <c r="U160" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V160" s="24" t="n"/>
-      <c r="W160" s="26" t="n"/>
-      <c r="X160" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V160" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W160" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X160" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y160" s="25" t="n"/>
       <c r="Z160" s="26" t="n"/>
       <c r="AA160" s="28" t="n"/>
       <c r="AB160" s="28" t="n"/>
-      <c r="AC160" s="30" t="n"/>
-      <c r="AD160" s="24" t="n"/>
+      <c r="AC160" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD160" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:03:43.336826Z</t>
+        </is>
+      </c>
       <c r="AE160" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.5700 (market_slug=aec-kbo-kti-sla-2026-10-06). Tie probability=0.0226.</t>
@@ -51414,7 +51596,7 @@
       </c>
       <c r="AG160" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH160" s="24" t="n"/>
@@ -51687,18 +51869,32 @@
       </c>
       <c r="U161" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V161" s="24" t="n"/>
-      <c r="W161" s="26" t="n"/>
-      <c r="X161" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V161" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W161" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X161" s="26" t="n">
+        <v>9</v>
+      </c>
       <c r="Y161" s="25" t="n"/>
       <c r="Z161" s="26" t="n"/>
       <c r="AA161" s="28" t="n"/>
       <c r="AB161" s="28" t="n"/>
-      <c r="AC161" s="30" t="n"/>
-      <c r="AD161" s="24" t="n"/>
+      <c r="AC161" s="30" t="n">
+        <v>-2</v>
+      </c>
+      <c r="AD161" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:03:45.747433Z</t>
+        </is>
+      </c>
       <c r="AE161" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.3800 (market_slug=aec-kbo-hea-sls-2026-10-06). Tie probability=0.0226.</t>
@@ -51711,7 +51907,7 @@
       </c>
       <c r="AG161" s="24" t="inlineStr">
         <is>
-          <t>not_applicable</t>
+          <t>review_required</t>
         </is>
       </c>
       <c r="AH161" s="24" t="n"/>
@@ -51984,18 +52180,32 @@
       </c>
       <c r="U162" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V162" s="24" t="n"/>
-      <c r="W162" s="26" t="n"/>
-      <c r="X162" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V162" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W162" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="X162" s="26" t="n">
+        <v>1</v>
+      </c>
       <c r="Y162" s="25" t="n"/>
       <c r="Z162" s="26" t="n"/>
       <c r="AA162" s="28" t="n"/>
       <c r="AB162" s="28" t="n"/>
-      <c r="AC162" s="30" t="n"/>
-      <c r="AD162" s="24" t="n"/>
+      <c r="AC162" s="30" t="n">
+        <v>0.4292</v>
+      </c>
+      <c r="AD162" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T16:03:48.172900Z</t>
+        </is>
+      </c>
       <c r="AE162" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.7000 (market_slug=aec-kbo-khi-kwt-2026-10-06). Tie probability=0.0226.</t>
@@ -52200,6 +52410,1491 @@
         </is>
       </c>
     </row>
+    <row r="163" ht="36" customHeight="1">
+      <c r="A163" s="24" t="inlineStr">
+        <is>
+          <t>62da44e9dbab4213</t>
+        </is>
+      </c>
+      <c r="B163" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:10.987601Z</t>
+        </is>
+      </c>
+      <c r="C163" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D163" s="24" t="inlineStr">
+        <is>
+          <t>141706</t>
+        </is>
+      </c>
+      <c r="E163" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F163" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="G163" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="H163" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I163" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J163" s="25" t="n"/>
+      <c r="K163" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L163" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="M163" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="N163" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="O163" s="28" t="n">
+        <v>0.581355</v>
+      </c>
+      <c r="P163" s="28" t="n"/>
+      <c r="Q163" s="28" t="n">
+        <v>0.031805</v>
+      </c>
+      <c r="R163" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="S163" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T163" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U163" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V163" s="24" t="n"/>
+      <c r="W163" s="26" t="n"/>
+      <c r="X163" s="26" t="n"/>
+      <c r="Y163" s="25" t="n"/>
+      <c r="Z163" s="26" t="n"/>
+      <c r="AA163" s="28" t="n"/>
+      <c r="AB163" s="28" t="n"/>
+      <c r="AC163" s="30" t="n"/>
+      <c r="AD163" s="24" t="n"/>
+      <c r="AE163" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-kbo-sls-ndc-2026-10-07). Tie probability=0.0226.</t>
+        </is>
+      </c>
+      <c r="AF163" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG163" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH163" s="24" t="n"/>
+      <c r="AI163" s="31" t="n"/>
+      <c r="AJ163" s="31" t="n"/>
+      <c r="AK163" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL163" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM163" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN163" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO163" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP163" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AQ163" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AR163" s="24" t="inlineStr">
+        <is>
+          <t>NC Dinos</t>
+        </is>
+      </c>
+      <c r="AS163" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AT163" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AU163" s="24" t="inlineStr">
+        <is>
+          <t>SSG Landers</t>
+        </is>
+      </c>
+      <c r="AV163" s="24" t="n"/>
+      <c r="AW163" s="24" t="n"/>
+      <c r="AX163" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY163" s="24" t="n"/>
+      <c r="AZ163" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA163" s="24" t="inlineStr">
+        <is>
+          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+        </is>
+      </c>
+      <c r="BB163" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC163" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD163" s="24" t="inlineStr">
+        <is>
+          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+        </is>
+      </c>
+      <c r="BE163" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF163" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG163" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH163" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:24:50.360101Z</t>
+        </is>
+      </c>
+      <c r="BI163" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ163" s="25" t="n"/>
+      <c r="BK163" s="26" t="n">
+        <v>-122</v>
+      </c>
+      <c r="BL163" s="27" t="n">
+        <v>1.819672</v>
+      </c>
+      <c r="BM163" s="28" t="n">
+        <v>0.54955</v>
+      </c>
+      <c r="BN163" s="28" t="n"/>
+      <c r="BO163" s="28" t="n"/>
+      <c r="BP163" s="25" t="n"/>
+      <c r="BQ163" s="27" t="n"/>
+      <c r="BR163" s="28" t="n"/>
+      <c r="BS163" s="28" t="n"/>
+      <c r="BT163" s="28" t="n"/>
+      <c r="BU163" s="25" t="n"/>
+      <c r="BV163" s="29" t="n"/>
+      <c r="BW163" s="24" t="n"/>
+      <c r="BX163" s="30" t="n"/>
+      <c r="BY163" s="27" t="n"/>
+      <c r="BZ163" s="24" t="n"/>
+      <c r="CA163" s="31" t="n"/>
+      <c r="CB163" s="24" t="n"/>
+      <c r="CC163" s="24" t="n"/>
+      <c r="CD163" s="24" t="n"/>
+      <c r="CE163" s="24" t="n"/>
+      <c r="CF163" s="24" t="n"/>
+      <c r="CG163" s="24" t="n"/>
+      <c r="CH163" s="24" t="n"/>
+      <c r="CI163" s="24" t="n"/>
+      <c r="CJ163" s="24" t="n"/>
+      <c r="CK163" s="24" t="n"/>
+      <c r="CL163" s="24" t="n"/>
+      <c r="CM163" s="24" t="n"/>
+      <c r="CN163" s="24" t="n"/>
+      <c r="CO163" s="24" t="n"/>
+      <c r="CP163" s="24" t="n"/>
+      <c r="CQ163" s="24" t="n"/>
+      <c r="CR163" s="24" t="n"/>
+      <c r="CS163" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT163" s="24" t="n"/>
+      <c r="CU163" s="24" t="n"/>
+      <c r="CV163" s="24" t="n"/>
+      <c r="CW163" s="24" t="n"/>
+      <c r="CX163" s="24" t="n"/>
+      <c r="CY163" s="24" t="n"/>
+      <c r="CZ163" s="24" t="n"/>
+      <c r="DA163" s="24" t="n"/>
+      <c r="DB163" s="24" t="n"/>
+      <c r="DC163" s="24" t="n"/>
+      <c r="DD163" s="24" t="n"/>
+      <c r="DE163" s="24" t="n"/>
+      <c r="DF163" s="24" t="n"/>
+      <c r="DG163" s="24" t="n"/>
+      <c r="DH163" s="24" t="n"/>
+      <c r="DI163" s="24" t="n"/>
+      <c r="DJ163" s="24" t="n"/>
+      <c r="DK163" s="24" t="n"/>
+      <c r="DL163" s="24" t="n"/>
+      <c r="DM163" s="24" t="n"/>
+      <c r="DN163" s="24" t="n"/>
+      <c r="DO163" s="24" t="n"/>
+      <c r="DP163" s="24" t="n"/>
+      <c r="DQ163" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114", "away_team": "NC Dinos", "draw_settlement_value": 0.5, "event_id": "141706", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1470.713142, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1509.096592}, "historical_source_observation_times_verified": false, "home_team": "SSG Landers", "inference_inputs": {"away_id": "NC", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"NC": 1470.713142, "SSG": 1509.096592}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "SSG", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.283322+00:00", "outcome_probabilities": {"away": 0.40733144859905934, "draw": 0.02262693, "home": 0.5700416214009406}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.418645, "home": 0.581355}, "snapshot_hash": "31f08db0170bc67e3172ab16f112bf6397329449d8875dba363f80213cb3ec33", "sport": "KBO"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="36" customHeight="1">
+      <c r="A164" s="24" t="inlineStr">
+        <is>
+          <t>ad6bec2479424e8d</t>
+        </is>
+      </c>
+      <c r="B164" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:10.987601Z</t>
+        </is>
+      </c>
+      <c r="C164" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D164" s="24" t="inlineStr">
+        <is>
+          <t>141707</t>
+        </is>
+      </c>
+      <c r="E164" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F164" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="G164" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="H164" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I164" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J164" s="25" t="n"/>
+      <c r="K164" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L164" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="M164" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="N164" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="O164" s="28" t="n">
+        <v>0.504038</v>
+      </c>
+      <c r="P164" s="28" t="n"/>
+      <c r="Q164" s="28" t="n">
+        <v>-0.066777</v>
+      </c>
+      <c r="R164" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S164" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T164" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U164" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V164" s="24" t="n"/>
+      <c r="W164" s="26" t="n"/>
+      <c r="X164" s="26" t="n"/>
+      <c r="Y164" s="25" t="n"/>
+      <c r="Z164" s="26" t="n"/>
+      <c r="AA164" s="28" t="n"/>
+      <c r="AB164" s="28" t="n"/>
+      <c r="AC164" s="30" t="n"/>
+      <c r="AD164" s="24" t="n"/>
+      <c r="AE164" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5700 (market_slug=aec-kbo-ltg-dbo-2026-10-07). Tie probability=0.0226.</t>
+        </is>
+      </c>
+      <c r="AF164" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG164" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH164" s="24" t="n"/>
+      <c r="AI164" s="31" t="n"/>
+      <c r="AJ164" s="31" t="n"/>
+      <c r="AK164" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL164" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM164" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN164" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO164" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP164" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AQ164" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AR164" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AS164" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AT164" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AU164" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AV164" s="24" t="n"/>
+      <c r="AW164" s="24" t="n"/>
+      <c r="AX164" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY164" s="24" t="n"/>
+      <c r="AZ164" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA164" s="24" t="inlineStr">
+        <is>
+          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+        </is>
+      </c>
+      <c r="BB164" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC164" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD164" s="24" t="inlineStr">
+        <is>
+          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+        </is>
+      </c>
+      <c r="BE164" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF164" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG164" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH164" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:24:50.421198Z</t>
+        </is>
+      </c>
+      <c r="BI164" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ164" s="25" t="n"/>
+      <c r="BK164" s="26" t="n">
+        <v>-133</v>
+      </c>
+      <c r="BL164" s="27" t="n">
+        <v>1.75188</v>
+      </c>
+      <c r="BM164" s="28" t="n">
+        <v>0.570815</v>
+      </c>
+      <c r="BN164" s="28" t="n"/>
+      <c r="BO164" s="28" t="n"/>
+      <c r="BP164" s="25" t="n"/>
+      <c r="BQ164" s="27" t="n"/>
+      <c r="BR164" s="28" t="n"/>
+      <c r="BS164" s="28" t="n"/>
+      <c r="BT164" s="28" t="n"/>
+      <c r="BU164" s="25" t="n"/>
+      <c r="BV164" s="29" t="n"/>
+      <c r="BW164" s="24" t="n"/>
+      <c r="BX164" s="30" t="n"/>
+      <c r="BY164" s="27" t="n"/>
+      <c r="BZ164" s="24" t="n"/>
+      <c r="CA164" s="31" t="n"/>
+      <c r="CB164" s="24" t="n"/>
+      <c r="CC164" s="24" t="n"/>
+      <c r="CD164" s="24" t="n"/>
+      <c r="CE164" s="24" t="n"/>
+      <c r="CF164" s="24" t="n"/>
+      <c r="CG164" s="24" t="n"/>
+      <c r="CH164" s="24" t="n"/>
+      <c r="CI164" s="24" t="n"/>
+      <c r="CJ164" s="24" t="n"/>
+      <c r="CK164" s="24" t="n"/>
+      <c r="CL164" s="24" t="n"/>
+      <c r="CM164" s="24" t="n"/>
+      <c r="CN164" s="24" t="n"/>
+      <c r="CO164" s="24" t="n"/>
+      <c r="CP164" s="24" t="n"/>
+      <c r="CQ164" s="24" t="n"/>
+      <c r="CR164" s="24" t="n"/>
+      <c r="CS164" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT164" s="24" t="n"/>
+      <c r="CU164" s="24" t="n"/>
+      <c r="CV164" s="24" t="n"/>
+      <c r="CW164" s="24" t="n"/>
+      <c r="CX164" s="24" t="n"/>
+      <c r="CY164" s="24" t="n"/>
+      <c r="CZ164" s="24" t="n"/>
+      <c r="DA164" s="24" t="n"/>
+      <c r="DB164" s="24" t="n"/>
+      <c r="DC164" s="24" t="n"/>
+      <c r="DD164" s="24" t="n"/>
+      <c r="DE164" s="24" t="n"/>
+      <c r="DF164" s="24" t="n"/>
+      <c r="DG164" s="24" t="n"/>
+      <c r="DH164" s="24" t="n"/>
+      <c r="DI164" s="24" t="n"/>
+      <c r="DJ164" s="24" t="n"/>
+      <c r="DK164" s="24" t="n"/>
+      <c r="DL164" s="24" t="n"/>
+      <c r="DM164" s="24" t="n"/>
+      <c r="DN164" s="24" t="n"/>
+      <c r="DO164" s="24" t="n"/>
+      <c r="DP164" s="24" t="n"/>
+      <c r="DQ164" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114", "away_team": "Doosan Bears", "draw_settlement_value": 0.5, "event_id": "141707", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1523.924017, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1506.794811}, "historical_source_observation_times_verified": false, "home_team": "LG Twins", "inference_inputs": {"away_id": "DOOSAN", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DOOSAN": 1523.924017, "LG": 1506.794811}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "LG", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.283322+00:00", "outcome_probabilities": {"away": 0.484648703228405, "draw": 0.02262693, "home": 0.492724366771595}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.495962, "home": 0.504038}, "snapshot_hash": "cf1df3745177e4ea6b73c766e3bd90118f6d77b3d5d0fa9466d332ae291e5a03", "sport": "KBO"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="36" customHeight="1">
+      <c r="A165" s="24" t="inlineStr">
+        <is>
+          <t>eeac7360664c4a91</t>
+        </is>
+      </c>
+      <c r="B165" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:10.987601Z</t>
+        </is>
+      </c>
+      <c r="C165" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D165" s="24" t="inlineStr">
+        <is>
+          <t>141708</t>
+        </is>
+      </c>
+      <c r="E165" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F165" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="G165" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="H165" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I165" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J165" s="25" t="n"/>
+      <c r="K165" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L165" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="M165" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="N165" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="O165" s="28" t="n">
+        <v>0.577223</v>
+      </c>
+      <c r="P165" s="28" t="n"/>
+      <c r="Q165" s="28" t="n">
+        <v>0.057992</v>
+      </c>
+      <c r="R165" s="26" t="n">
+        <v>49</v>
+      </c>
+      <c r="S165" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T165" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U165" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V165" s="24" t="n"/>
+      <c r="W165" s="26" t="n"/>
+      <c r="X165" s="26" t="n"/>
+      <c r="Y165" s="25" t="n"/>
+      <c r="Z165" s="26" t="n"/>
+      <c r="AA165" s="28" t="n"/>
+      <c r="AB165" s="28" t="n"/>
+      <c r="AC165" s="30" t="n"/>
+      <c r="AD165" s="24" t="n"/>
+      <c r="AE165" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5200 (market_slug=aec-kbo-kwt-sla-2026-10-07). Tie probability=0.0226.</t>
+        </is>
+      </c>
+      <c r="AF165" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG165" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH165" s="24" t="n"/>
+      <c r="AI165" s="31" t="n"/>
+      <c r="AJ165" s="31" t="n"/>
+      <c r="AK165" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL165" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM165" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN165" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO165" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP165" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AQ165" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AR165" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AS165" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AT165" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AU165" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AV165" s="24" t="n"/>
+      <c r="AW165" s="24" t="n"/>
+      <c r="AX165" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY165" s="24" t="n"/>
+      <c r="AZ165" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA165" s="24" t="inlineStr">
+        <is>
+          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+        </is>
+      </c>
+      <c r="BB165" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC165" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD165" s="24" t="inlineStr">
+        <is>
+          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+        </is>
+      </c>
+      <c r="BE165" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF165" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG165" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH165" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:24:50.489684Z</t>
+        </is>
+      </c>
+      <c r="BI165" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ165" s="25" t="n"/>
+      <c r="BK165" s="26" t="n">
+        <v>-108</v>
+      </c>
+      <c r="BL165" s="27" t="n">
+        <v>1.925926</v>
+      </c>
+      <c r="BM165" s="28" t="n">
+        <v>0.519231</v>
+      </c>
+      <c r="BN165" s="28" t="n"/>
+      <c r="BO165" s="28" t="n"/>
+      <c r="BP165" s="25" t="n"/>
+      <c r="BQ165" s="27" t="n"/>
+      <c r="BR165" s="28" t="n"/>
+      <c r="BS165" s="28" t="n"/>
+      <c r="BT165" s="28" t="n"/>
+      <c r="BU165" s="25" t="n"/>
+      <c r="BV165" s="29" t="n"/>
+      <c r="BW165" s="24" t="n"/>
+      <c r="BX165" s="30" t="n"/>
+      <c r="BY165" s="27" t="n"/>
+      <c r="BZ165" s="24" t="n"/>
+      <c r="CA165" s="31" t="n"/>
+      <c r="CB165" s="24" t="n"/>
+      <c r="CC165" s="24" t="n"/>
+      <c r="CD165" s="24" t="n"/>
+      <c r="CE165" s="24" t="n"/>
+      <c r="CF165" s="24" t="n"/>
+      <c r="CG165" s="24" t="n"/>
+      <c r="CH165" s="24" t="n"/>
+      <c r="CI165" s="24" t="n"/>
+      <c r="CJ165" s="24" t="n"/>
+      <c r="CK165" s="24" t="n"/>
+      <c r="CL165" s="24" t="n"/>
+      <c r="CM165" s="24" t="n"/>
+      <c r="CN165" s="24" t="n"/>
+      <c r="CO165" s="24" t="n"/>
+      <c r="CP165" s="24" t="n"/>
+      <c r="CQ165" s="24" t="n"/>
+      <c r="CR165" s="24" t="n"/>
+      <c r="CS165" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT165" s="24" t="n"/>
+      <c r="CU165" s="24" t="n"/>
+      <c r="CV165" s="24" t="n"/>
+      <c r="CW165" s="24" t="n"/>
+      <c r="CX165" s="24" t="n"/>
+      <c r="CY165" s="24" t="n"/>
+      <c r="CZ165" s="24" t="n"/>
+      <c r="DA165" s="24" t="n"/>
+      <c r="DB165" s="24" t="n"/>
+      <c r="DC165" s="24" t="n"/>
+      <c r="DD165" s="24" t="n"/>
+      <c r="DE165" s="24" t="n"/>
+      <c r="DF165" s="24" t="n"/>
+      <c r="DG165" s="24" t="n"/>
+      <c r="DH165" s="24" t="n"/>
+      <c r="DI165" s="24" t="n"/>
+      <c r="DJ165" s="24" t="n"/>
+      <c r="DK165" s="24" t="n"/>
+      <c r="DL165" s="24" t="n"/>
+      <c r="DM165" s="24" t="n"/>
+      <c r="DN165" s="24" t="n"/>
+      <c r="DO165" s="24" t="n"/>
+      <c r="DP165" s="24" t="n"/>
+      <c r="DQ165" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114", "away_team": "Samsung Lions", "draw_settlement_value": 0.5, "event_id": "141708", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1543.670103, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1579.036662}, "historical_source_observation_times_verified": false, "home_team": "KT Wiz", "inference_inputs": {"away_id": "SAMSUNG", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"KT": 1579.036662, "SAMSUNG": 1543.670103}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "KT", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.283322+00:00", "outcome_probabilities": {"away": 0.4114631296070524, "draw": 0.02262693, "home": 0.5659099403929476}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.422777, "home": 0.577223}, "snapshot_hash": "3fae4502ed3b14dbbf2cf166b4d67390c55d456648b342cdafced37495eacc0f", "sport": "KBO"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="36" customHeight="1">
+      <c r="A166" s="24" t="inlineStr">
+        <is>
+          <t>fc1d0965db9e40ef</t>
+        </is>
+      </c>
+      <c r="B166" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:10.987601Z</t>
+        </is>
+      </c>
+      <c r="C166" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D166" s="24" t="inlineStr">
+        <is>
+          <t>141709</t>
+        </is>
+      </c>
+      <c r="E166" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F166" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="G166" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="H166" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I166" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J166" s="25" t="n"/>
+      <c r="K166" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L166" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="M166" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="N166" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="O166" s="28" t="n">
+        <v>0.5302480000000001</v>
+      </c>
+      <c r="P166" s="28" t="n"/>
+      <c r="Q166" s="28" t="n">
+        <v>-0.08952400000000001</v>
+      </c>
+      <c r="R166" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S166" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T166" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U166" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V166" s="24" t="n"/>
+      <c r="W166" s="26" t="n"/>
+      <c r="X166" s="26" t="n"/>
+      <c r="Y166" s="25" t="n"/>
+      <c r="Z166" s="26" t="n"/>
+      <c r="AA166" s="28" t="n"/>
+      <c r="AB166" s="28" t="n"/>
+      <c r="AC166" s="30" t="n"/>
+      <c r="AD166" s="24" t="n"/>
+      <c r="AE166" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6200 (market_slug=aec-kbo-lgo-kti-2026-10-07). Tie probability=0.0226.</t>
+        </is>
+      </c>
+      <c r="AF166" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG166" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH166" s="24" t="n"/>
+      <c r="AI166" s="31" t="n"/>
+      <c r="AJ166" s="31" t="n"/>
+      <c r="AK166" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL166" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM166" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN166" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO166" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP166" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AQ166" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AR166" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AS166" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AT166" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AU166" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AV166" s="24" t="n"/>
+      <c r="AW166" s="24" t="n"/>
+      <c r="AX166" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY166" s="24" t="n"/>
+      <c r="AZ166" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA166" s="24" t="inlineStr">
+        <is>
+          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+        </is>
+      </c>
+      <c r="BB166" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC166" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD166" s="24" t="inlineStr">
+        <is>
+          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+        </is>
+      </c>
+      <c r="BE166" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF166" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG166" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH166" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:24:50.570264Z</t>
+        </is>
+      </c>
+      <c r="BI166" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ166" s="25" t="n"/>
+      <c r="BK166" s="26" t="n">
+        <v>-163</v>
+      </c>
+      <c r="BL166" s="27" t="n">
+        <v>1.613497</v>
+      </c>
+      <c r="BM166" s="28" t="n">
+        <v>0.619772</v>
+      </c>
+      <c r="BN166" s="28" t="n"/>
+      <c r="BO166" s="28" t="n"/>
+      <c r="BP166" s="25" t="n"/>
+      <c r="BQ166" s="27" t="n"/>
+      <c r="BR166" s="28" t="n"/>
+      <c r="BS166" s="28" t="n"/>
+      <c r="BT166" s="28" t="n"/>
+      <c r="BU166" s="25" t="n"/>
+      <c r="BV166" s="29" t="n"/>
+      <c r="BW166" s="24" t="n"/>
+      <c r="BX166" s="30" t="n"/>
+      <c r="BY166" s="27" t="n"/>
+      <c r="BZ166" s="24" t="n"/>
+      <c r="CA166" s="31" t="n"/>
+      <c r="CB166" s="24" t="n"/>
+      <c r="CC166" s="24" t="n"/>
+      <c r="CD166" s="24" t="n"/>
+      <c r="CE166" s="24" t="n"/>
+      <c r="CF166" s="24" t="n"/>
+      <c r="CG166" s="24" t="n"/>
+      <c r="CH166" s="24" t="n"/>
+      <c r="CI166" s="24" t="n"/>
+      <c r="CJ166" s="24" t="n"/>
+      <c r="CK166" s="24" t="n"/>
+      <c r="CL166" s="24" t="n"/>
+      <c r="CM166" s="24" t="n"/>
+      <c r="CN166" s="24" t="n"/>
+      <c r="CO166" s="24" t="n"/>
+      <c r="CP166" s="24" t="n"/>
+      <c r="CQ166" s="24" t="n"/>
+      <c r="CR166" s="24" t="n"/>
+      <c r="CS166" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT166" s="24" t="n"/>
+      <c r="CU166" s="24" t="n"/>
+      <c r="CV166" s="24" t="n"/>
+      <c r="CW166" s="24" t="n"/>
+      <c r="CX166" s="24" t="n"/>
+      <c r="CY166" s="24" t="n"/>
+      <c r="CZ166" s="24" t="n"/>
+      <c r="DA166" s="24" t="n"/>
+      <c r="DB166" s="24" t="n"/>
+      <c r="DC166" s="24" t="n"/>
+      <c r="DD166" s="24" t="n"/>
+      <c r="DE166" s="24" t="n"/>
+      <c r="DF166" s="24" t="n"/>
+      <c r="DG166" s="24" t="n"/>
+      <c r="DH166" s="24" t="n"/>
+      <c r="DI166" s="24" t="n"/>
+      <c r="DJ166" s="24" t="n"/>
+      <c r="DK166" s="24" t="n"/>
+      <c r="DL166" s="24" t="n"/>
+      <c r="DM166" s="24" t="n"/>
+      <c r="DN166" s="24" t="n"/>
+      <c r="DO166" s="24" t="n"/>
+      <c r="DP166" s="24" t="n"/>
+      <c r="DQ166" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114", "away_team": "Kia Tigers", "draw_settlement_value": 0.5, "event_id": "141709", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1524.366838, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1482.834576}, "historical_source_observation_times_verified": false, "home_team": "Lotte Giants", "inference_inputs": {"away_id": "KIA", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"KIA": 1524.366838, "LOTTE": 1482.834576}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "LOTTE", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.283322+00:00", "outcome_probabilities": {"away": 0.5189340850239297, "draw": 0.02262693, "home": 0.4584389849760702}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.530248, "home": 0.469752}, "snapshot_hash": "7224fd777d486ed64d33b68c30084e68ac7193ae5a6ee397c4e0e18c916f3b21", "sport": "KBO"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="36" customHeight="1">
+      <c r="A167" s="24" t="inlineStr">
+        <is>
+          <t>45135b7cf1c746d1</t>
+        </is>
+      </c>
+      <c r="B167" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:10.987601Z</t>
+        </is>
+      </c>
+      <c r="C167" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D167" s="24" t="inlineStr">
+        <is>
+          <t>141710</t>
+        </is>
+      </c>
+      <c r="E167" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F167" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="G167" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="H167" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I167" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J167" s="25" t="n"/>
+      <c r="K167" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L167" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="M167" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="N167" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="O167" s="28" t="n">
+        <v>0.530326</v>
+      </c>
+      <c r="P167" s="28" t="n"/>
+      <c r="Q167" s="28" t="n">
+        <v>0.12049</v>
+      </c>
+      <c r="R167" s="26" t="n">
+        <v>80</v>
+      </c>
+      <c r="S167" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T167" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U167" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V167" s="24" t="n"/>
+      <c r="W167" s="26" t="n"/>
+      <c r="X167" s="26" t="n"/>
+      <c r="Y167" s="25" t="n"/>
+      <c r="Z167" s="26" t="n"/>
+      <c r="AA167" s="28" t="n"/>
+      <c r="AB167" s="28" t="n"/>
+      <c r="AC167" s="30" t="n"/>
+      <c r="AD167" s="24" t="n"/>
+      <c r="AE167" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4100 (market_slug=aec-kbo-khi-hea-2026-10-07). Tie probability=0.0226.</t>
+        </is>
+      </c>
+      <c r="AF167" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG167" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH167" s="24" t="n"/>
+      <c r="AI167" s="31" t="n"/>
+      <c r="AJ167" s="31" t="n"/>
+      <c r="AK167" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL167" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM167" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN167" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO167" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP167" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AQ167" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AR167" s="24" t="inlineStr">
+        <is>
+          <t>Hanwha Eagles</t>
+        </is>
+      </c>
+      <c r="AS167" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AT167" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AU167" s="24" t="inlineStr">
+        <is>
+          <t>Kiwoom Heroes</t>
+        </is>
+      </c>
+      <c r="AV167" s="24" t="n"/>
+      <c r="AW167" s="24" t="n"/>
+      <c r="AX167" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY167" s="24" t="n"/>
+      <c r="AZ167" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA167" s="24" t="inlineStr">
+        <is>
+          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+        </is>
+      </c>
+      <c r="BB167" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC167" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD167" s="24" t="inlineStr">
+        <is>
+          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+        </is>
+      </c>
+      <c r="BE167" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF167" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG167" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH167" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-06T22:25:10.987601Z</t>
+        </is>
+      </c>
+      <c r="BI167" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ167" s="25" t="n"/>
+      <c r="BK167" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="BL167" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BM167" s="28" t="n">
+        <v>0.409836</v>
+      </c>
+      <c r="BN167" s="28" t="n"/>
+      <c r="BO167" s="28" t="n"/>
+      <c r="BP167" s="25" t="n"/>
+      <c r="BQ167" s="27" t="n"/>
+      <c r="BR167" s="28" t="n"/>
+      <c r="BS167" s="28" t="n"/>
+      <c r="BT167" s="28" t="n"/>
+      <c r="BU167" s="25" t="n"/>
+      <c r="BV167" s="29" t="n"/>
+      <c r="BW167" s="24" t="n"/>
+      <c r="BX167" s="30" t="n"/>
+      <c r="BY167" s="27" t="n"/>
+      <c r="BZ167" s="24" t="n"/>
+      <c r="CA167" s="31" t="n"/>
+      <c r="CB167" s="24" t="n"/>
+      <c r="CC167" s="24" t="n"/>
+      <c r="CD167" s="24" t="n"/>
+      <c r="CE167" s="24" t="n"/>
+      <c r="CF167" s="24" t="n"/>
+      <c r="CG167" s="24" t="n"/>
+      <c r="CH167" s="24" t="n"/>
+      <c r="CI167" s="24" t="n"/>
+      <c r="CJ167" s="24" t="n"/>
+      <c r="CK167" s="24" t="n"/>
+      <c r="CL167" s="24" t="n"/>
+      <c r="CM167" s="24" t="n"/>
+      <c r="CN167" s="24" t="n"/>
+      <c r="CO167" s="24" t="n"/>
+      <c r="CP167" s="24" t="n"/>
+      <c r="CQ167" s="24" t="n"/>
+      <c r="CR167" s="24" t="n"/>
+      <c r="CS167" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT167" s="24" t="n"/>
+      <c r="CU167" s="24" t="n"/>
+      <c r="CV167" s="24" t="n"/>
+      <c r="CW167" s="24" t="n"/>
+      <c r="CX167" s="24" t="n"/>
+      <c r="CY167" s="24" t="n"/>
+      <c r="CZ167" s="24" t="n"/>
+      <c r="DA167" s="24" t="n"/>
+      <c r="DB167" s="24" t="n"/>
+      <c r="DC167" s="24" t="n"/>
+      <c r="DD167" s="24" t="n"/>
+      <c r="DE167" s="24" t="n"/>
+      <c r="DF167" s="24" t="n"/>
+      <c r="DG167" s="24" t="n"/>
+      <c r="DH167" s="24" t="n"/>
+      <c r="DI167" s="24" t="n"/>
+      <c r="DJ167" s="24" t="n"/>
+      <c r="DK167" s="24" t="n"/>
+      <c r="DL167" s="24" t="n"/>
+      <c r="DM167" s="24" t="n"/>
+      <c r="DN167" s="24" t="n"/>
+      <c r="DO167" s="24" t="n"/>
+      <c r="DP167" s="24" t="n"/>
+      <c r="DQ167" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114", "away_team": "Hanwha Eagles", "draw_settlement_value": 0.5, "event_id": "141710", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1438.436026, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1440.024074}, "historical_source_observation_times_verified": false, "home_team": "Kiwoom Heroes", "inference_inputs": {"away_id": "HANWHA", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"HANWHA": 1438.436026, "KIWOOM": 1440.024074}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "KIWOOM", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.283322+00:00", "outcome_probabilities": {"away": 0.45836082040103526, "draw": 0.02262693, "home": 0.5190122495989647}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.469674, "home": 0.530326}, "snapshot_hash": "322b7cf15492d4f871004a8d048c4176fc52dec89f029ce76c72682e2d17a07b", "sport": "KBO"}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="0" fitToWidth="1"/>

--- a/data/sports/kbo/research.xlsx
+++ b/data/sports/kbo/research.xlsx
@@ -300,8 +300,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ167" headerRowCount="1">
-  <autoFilter ref="A1:DQ167"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="PicksLedger" displayName="PicksLedger" ref="A1:DQ173" headerRowCount="1">
+  <autoFilter ref="A1:DQ173"/>
   <tableColumns count="121">
     <tableColumn id="1" name="pick_id"/>
     <tableColumn id="2" name="created_at_utc"/>
@@ -780,19 +780,19 @@
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="6">
-        <f>COUNTA('Picks'!$A$2:$A$167)</f>
+        <f>COUNTA('Picks'!$A$2:$A$173)</f>
         <v/>
       </c>
       <c r="C4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$167,"open")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$173,"open")</f>
         <v/>
       </c>
       <c r="E4" s="6">
-        <f>COUNTIF('Picks'!$U$2:$U$167,"settled")</f>
+        <f>COUNTIF('Picks'!$U$2:$U$173,"settled")</f>
         <v/>
       </c>
       <c r="G4" s="6">
-        <f>IF(COUNTIFS('Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"win")+COUNTIFS('Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
+        <f>IF(COUNTIFS('Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"win")+COUNTIFS('Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"loss")&gt;=$L$2,"Ready","Insufficient sample")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +820,19 @@
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="6">
-        <f>COUNTIF('Picks'!$BX$2:$BX$167,"&gt;0")</f>
+        <f>COUNTIF('Picks'!$BX$2:$BX$173,"&gt;0")</f>
         <v/>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIFS('Picks'!$BX$2:$BX$167,"&gt;0",'Picks'!$V$2:$V$167,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$167,"&gt;0",'Picks'!$V$2:$V$167,"loss")</f>
+        <f>COUNTIFS('Picks'!$BX$2:$BX$173,"&gt;0",'Picks'!$V$2:$V$173,"win")&amp;"-"&amp;COUNTIFS('Picks'!$BX$2:$BX$173,"&gt;0",'Picks'!$V$2:$V$173,"loss")</f>
         <v/>
       </c>
       <c r="E7" s="7">
-        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$167,"&gt;0",'Picks'!$V$2:$V$167,"win")/(COUNTIFS('Picks'!$BX$2:$BX$167,"&gt;0",'Picks'!$V$2:$V$167,"win")+COUNTIFS('Picks'!$BX$2:$BX$167,"&gt;0",'Picks'!$V$2:$V$167,"loss")),0)</f>
+        <f>IFERROR(COUNTIFS('Picks'!$BX$2:$BX$173,"&gt;0",'Picks'!$V$2:$V$173,"win")/(COUNTIFS('Picks'!$BX$2:$BX$173,"&gt;0",'Picks'!$V$2:$V$173,"win")+COUNTIFS('Picks'!$BX$2:$BX$173,"&gt;0",'Picks'!$V$2:$V$173,"loss")),0)</f>
         <v/>
       </c>
       <c r="G7" s="7">
-        <f>IFERROR(SUM('Picks'!$BY$2:$BY$167)/SUM('Picks'!$BX$2:$BX$167),0)</f>
+        <f>IFERROR(SUM('Picks'!$BY$2:$BY$173)/SUM('Picks'!$BX$2:$BX$173),0)</f>
         <v/>
       </c>
     </row>
@@ -860,19 +860,19 @@
     </row>
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="8">
-        <f>SUM('Picks'!$BY$2:$BY$167)</f>
+        <f>SUM('Picks'!$BY$2:$BY$173)</f>
         <v/>
       </c>
       <c r="C10" s="9">
-        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$167,"&lt;&gt;",'Picks'!$AB$2:$AB$167),0)</f>
+        <f>IFERROR(AVERAGEIF('Picks'!$AB$2:$AB$173,"&lt;&gt;",'Picks'!$AB$2:$AB$173),0)</f>
         <v/>
       </c>
       <c r="E10" s="6">
-        <f>COUNTIFS('Picks'!$AM$2:$AM$167,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$167,"settled")</f>
+        <f>COUNTIFS('Picks'!$AM$2:$AM$173,"QUALIFIED_SHADOW_CALL",'Picks'!$U$2:$U$173,"settled")</f>
         <v/>
       </c>
       <c r="G10" s="8">
-        <f>SUMIFS('Picks'!$AC$2:$AC$167,'Picks'!$AM$2:$AM$167,"QUALIFIED_SHADOW_CALL")</f>
+        <f>SUMIFS('Picks'!$AC$2:$AC$173,'Picks'!$AM$2:$AM$173,"QUALIFIED_SHADOW_CALL")</f>
         <v/>
       </c>
     </row>
@@ -927,15 +927,15 @@
         </is>
       </c>
       <c r="B14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$167,$A14,'Picks'!$U$2:$U$167,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A14,'Picks'!$U$2:$U$173,"settled")</f>
         <v/>
       </c>
       <c r="C14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$167,$A14,'Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A14,'Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"win")</f>
         <v/>
       </c>
       <c r="D14" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$167,$A14,'Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A14,'Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"loss")</f>
         <v/>
       </c>
       <c r="E14" s="14">
@@ -943,11 +943,11 @@
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$167,'Picks'!$H$2:$H$167,$A14)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$173,'Picks'!$H$2:$H$173,$A14)</f>
         <v/>
       </c>
       <c r="G14" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$167,'Picks'!$H$2:$H$167,$A14,'Picks'!$U$2:$U$167,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$173,'Picks'!$H$2:$H$173,$A14,'Picks'!$U$2:$U$173,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -958,15 +958,15 @@
         </is>
       </c>
       <c r="B15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$167,$A15,'Picks'!$U$2:$U$167,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A15,'Picks'!$U$2:$U$173,"settled")</f>
         <v/>
       </c>
       <c r="C15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$167,$A15,'Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A15,'Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"win")</f>
         <v/>
       </c>
       <c r="D15" s="18">
-        <f>COUNTIFS('Picks'!$H$2:$H$167,$A15,'Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A15,'Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"loss")</f>
         <v/>
       </c>
       <c r="E15" s="19">
@@ -974,11 +974,11 @@
         <v/>
       </c>
       <c r="F15" s="20">
-        <f>SUMIFS('Picks'!$BY$2:$BY$167,'Picks'!$H$2:$H$167,$A15)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$173,'Picks'!$H$2:$H$173,$A15)</f>
         <v/>
       </c>
       <c r="G15" s="21">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$167,'Picks'!$H$2:$H$167,$A15,'Picks'!$U$2:$U$167,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$173,'Picks'!$H$2:$H$173,$A15,'Picks'!$U$2:$U$173,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -989,15 +989,15 @@
         </is>
       </c>
       <c r="B16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$167,$A16,'Picks'!$U$2:$U$167,"settled")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A16,'Picks'!$U$2:$U$173,"settled")</f>
         <v/>
       </c>
       <c r="C16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$167,$A16,'Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"win")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A16,'Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"win")</f>
         <v/>
       </c>
       <c r="D16" s="13">
-        <f>COUNTIFS('Picks'!$H$2:$H$167,$A16,'Picks'!$U$2:$U$167,"settled",'Picks'!$V$2:$V$167,"loss")</f>
+        <f>COUNTIFS('Picks'!$H$2:$H$173,$A16,'Picks'!$U$2:$U$173,"settled",'Picks'!$V$2:$V$173,"loss")</f>
         <v/>
       </c>
       <c r="E16" s="14">
@@ -1005,11 +1005,11 @@
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>SUMIFS('Picks'!$BY$2:$BY$167,'Picks'!$H$2:$H$167,$A16)</f>
+        <f>SUMIFS('Picks'!$BY$2:$BY$173,'Picks'!$H$2:$H$173,$A16)</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$167,'Picks'!$H$2:$H$167,$A16,'Picks'!$U$2:$U$167,"settled"),0)</f>
+        <f>IFERROR(AVERAGEIFS('Picks'!$AB$2:$AB$173,'Picks'!$H$2:$H$173,$A16,'Picks'!$U$2:$U$173,"settled"),0)</f>
         <v/>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:DQ167"/>
+  <dimension ref="A1:DQ173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -52413,12 +52413,12 @@
     <row r="163" ht="36" customHeight="1">
       <c r="A163" s="24" t="inlineStr">
         <is>
-          <t>62da44e9dbab4213</t>
+          <t>cef40ab878c84919</t>
         </is>
       </c>
       <c r="B163" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:10.987601Z</t>
+          <t>2026-10-07T05:28:43.252505Z</t>
         </is>
       </c>
       <c r="C163" s="24" t="inlineStr">
@@ -52463,23 +52463,23 @@
         </is>
       </c>
       <c r="L163" s="26" t="n">
-        <v>-122</v>
+        <v>-144</v>
       </c>
       <c r="M163" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.694444</v>
       </c>
       <c r="N163" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.590164</v>
       </c>
       <c r="O163" s="28" t="n">
         <v>0.581355</v>
       </c>
       <c r="P163" s="28" t="n"/>
       <c r="Q163" s="28" t="n">
-        <v>0.031805</v>
+        <v>-0.008809000000000001</v>
       </c>
       <c r="R163" s="26" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="S163" s="29" t="n">
         <v>1</v>
@@ -52491,21 +52491,41 @@
       </c>
       <c r="U163" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V163" s="24" t="n"/>
-      <c r="W163" s="26" t="n"/>
-      <c r="X163" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V163" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W163" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X163" s="26" t="n">
+        <v>6</v>
+      </c>
       <c r="Y163" s="25" t="n"/>
-      <c r="Z163" s="26" t="n"/>
-      <c r="AA163" s="28" t="n"/>
-      <c r="AB163" s="28" t="n"/>
-      <c r="AC163" s="30" t="n"/>
-      <c r="AD163" s="24" t="n"/>
+      <c r="Z163" s="26" t="n">
+        <v>-138</v>
+      </c>
+      <c r="AA163" s="28" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="AB163" s="28" t="n">
+        <v>-0.010164</v>
+      </c>
+      <c r="AC163" s="30" t="n">
+        <v>0.6944</v>
+      </c>
+      <c r="AD163" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:04:50.745776Z</t>
+        </is>
+      </c>
       <c r="AE163" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.5500 (market_slug=aec-kbo-sls-ndc-2026-10-07). Tie probability=0.0226.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.5900 (market_slug=aec-kbo-sls-ndc-2026-10-07). Tie probability=0.0226.</t>
         </is>
       </c>
       <c r="AF163" s="31" t="inlineStr">
@@ -52589,7 +52609,7 @@
       </c>
       <c r="BA163" s="24" t="inlineStr">
         <is>
-          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+          <t>72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a</t>
         </is>
       </c>
       <c r="BB163" s="24" t="inlineStr">
@@ -52604,7 +52624,7 @@
       </c>
       <c r="BD163" s="24" t="inlineStr">
         <is>
-          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+          <t>72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a</t>
         </is>
       </c>
       <c r="BE163" s="24" t="inlineStr">
@@ -52624,7 +52644,7 @@
       </c>
       <c r="BH163" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:24:50.360101Z</t>
+          <t>2026-10-07T05:28:32.692035Z</t>
         </is>
       </c>
       <c r="BI163" s="24" t="inlineStr">
@@ -52634,19 +52654,23 @@
       </c>
       <c r="BJ163" s="25" t="n"/>
       <c r="BK163" s="26" t="n">
-        <v>-122</v>
+        <v>-144</v>
       </c>
       <c r="BL163" s="27" t="n">
-        <v>1.819672</v>
+        <v>1.694444</v>
       </c>
       <c r="BM163" s="28" t="n">
-        <v>0.54955</v>
+        <v>0.590164</v>
       </c>
       <c r="BN163" s="28" t="n"/>
       <c r="BO163" s="28" t="n"/>
       <c r="BP163" s="25" t="n"/>
-      <c r="BQ163" s="27" t="n"/>
-      <c r="BR163" s="28" t="n"/>
+      <c r="BQ163" s="27" t="n">
+        <v>1.724638</v>
+      </c>
+      <c r="BR163" s="28" t="n">
+        <v>0.58</v>
+      </c>
       <c r="BS163" s="28" t="n"/>
       <c r="BT163" s="28" t="n"/>
       <c r="BU163" s="25" t="n"/>
@@ -52675,7 +52699,7 @@
       <c r="CR163" s="24" t="n"/>
       <c r="CS163" s="24" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="CT163" s="24" t="n"/>
@@ -52703,19 +52727,19 @@
       <c r="DP163" s="24" t="n"/>
       <c r="DQ163" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114", "away_team": "NC Dinos", "draw_settlement_value": 0.5, "event_id": "141706", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1470.713142, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1509.096592}, "historical_source_observation_times_verified": false, "home_team": "SSG Landers", "inference_inputs": {"away_id": "NC", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"NC": 1470.713142, "SSG": 1509.096592}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "SSG", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.283322+00:00", "outcome_probabilities": {"away": 0.40733144859905934, "draw": 0.02262693, "home": 0.5700416214009406}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.418645, "home": 0.581355}, "snapshot_hash": "31f08db0170bc67e3172ab16f112bf6397329449d8875dba363f80213cb3ec33", "sport": "KBO"}</t>
+          <t>{"artifact_hash": "72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a", "away_team": "NC Dinos", "draw_settlement_value": 0.5, "event_id": "141706", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1470.713142, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1509.096592}, "historical_source_observation_times_verified": false, "home_team": "SSG Landers", "inference_inputs": {"away_id": "NC", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"NC": 1470.713142, "SSG": 1509.096592}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "58ea522476e21dc70a719fe60647c19a772fcb4703fef8ed2d47c4ba7f07c2d5"}, "home_id": "SSG", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-07T05:28:32.629666+00:00", "outcome_probabilities": {"away": 0.40733144859905934, "draw": 0.02262693, "home": 0.5700416214009406}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.418645, "home": 0.581355}, "snapshot_hash": "28dce38d0fc15f142228f9a356b5c6fdace64c9534c3a07f255be023a4118dfc", "sport": "KBO"}</t>
         </is>
       </c>
     </row>
     <row r="164" ht="36" customHeight="1">
       <c r="A164" s="24" t="inlineStr">
         <is>
-          <t>ad6bec2479424e8d</t>
+          <t>9da89d4e9024455d</t>
         </is>
       </c>
       <c r="B164" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:10.987601Z</t>
+          <t>2026-10-07T05:28:43.252505Z</t>
         </is>
       </c>
       <c r="C164" s="24" t="inlineStr">
@@ -52760,20 +52784,20 @@
         </is>
       </c>
       <c r="L164" s="26" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="M164" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.787402</v>
       </c>
       <c r="N164" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="O164" s="28" t="n">
         <v>0.504038</v>
       </c>
       <c r="P164" s="28" t="n"/>
       <c r="Q164" s="28" t="n">
-        <v>-0.066777</v>
+        <v>-0.055433</v>
       </c>
       <c r="R164" s="26" t="n">
         <v>0</v>
@@ -52788,21 +52812,41 @@
       </c>
       <c r="U164" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V164" s="24" t="n"/>
-      <c r="W164" s="26" t="n"/>
-      <c r="X164" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V164" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W164" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X164" s="26" t="n">
+        <v>7</v>
+      </c>
       <c r="Y164" s="25" t="n"/>
-      <c r="Z164" s="26" t="n"/>
-      <c r="AA164" s="28" t="n"/>
-      <c r="AB164" s="28" t="n"/>
-      <c r="AC164" s="30" t="n"/>
-      <c r="AD164" s="24" t="n"/>
+      <c r="Z164" s="26" t="n">
+        <v>-127</v>
+      </c>
+      <c r="AA164" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB164" s="28" t="n">
+        <v>0.000529</v>
+      </c>
+      <c r="AC164" s="30" t="n">
+        <v>0.7874</v>
+      </c>
+      <c r="AD164" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:04:51.947570Z</t>
+        </is>
+      </c>
       <c r="AE164" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.5700 (market_slug=aec-kbo-ltg-dbo-2026-10-07). Tie probability=0.0226.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.5600 (market_slug=aec-kbo-ltg-dbo-2026-10-07). Tie probability=0.0226.</t>
         </is>
       </c>
       <c r="AF164" s="31" t="inlineStr">
@@ -52886,7 +52930,7 @@
       </c>
       <c r="BA164" s="24" t="inlineStr">
         <is>
-          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+          <t>72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a</t>
         </is>
       </c>
       <c r="BB164" s="24" t="inlineStr">
@@ -52901,7 +52945,7 @@
       </c>
       <c r="BD164" s="24" t="inlineStr">
         <is>
-          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+          <t>72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a</t>
         </is>
       </c>
       <c r="BE164" s="24" t="inlineStr">
@@ -52921,7 +52965,7 @@
       </c>
       <c r="BH164" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:24:50.421198Z</t>
+          <t>2026-10-07T05:28:32.757030Z</t>
         </is>
       </c>
       <c r="BI164" s="24" t="inlineStr">
@@ -52931,19 +52975,23 @@
       </c>
       <c r="BJ164" s="25" t="n"/>
       <c r="BK164" s="26" t="n">
-        <v>-133</v>
+        <v>-127</v>
       </c>
       <c r="BL164" s="27" t="n">
-        <v>1.75188</v>
+        <v>1.787402</v>
       </c>
       <c r="BM164" s="28" t="n">
-        <v>0.570815</v>
+        <v>0.5594710000000001</v>
       </c>
       <c r="BN164" s="28" t="n"/>
       <c r="BO164" s="28" t="n"/>
       <c r="BP164" s="25" t="n"/>
-      <c r="BQ164" s="27" t="n"/>
-      <c r="BR164" s="28" t="n"/>
+      <c r="BQ164" s="27" t="n">
+        <v>1.787402</v>
+      </c>
+      <c r="BR164" s="28" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="BS164" s="28" t="n"/>
       <c r="BT164" s="28" t="n"/>
       <c r="BU164" s="25" t="n"/>
@@ -53000,19 +53048,19 @@
       <c r="DP164" s="24" t="n"/>
       <c r="DQ164" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114", "away_team": "Doosan Bears", "draw_settlement_value": 0.5, "event_id": "141707", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1523.924017, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1506.794811}, "historical_source_observation_times_verified": false, "home_team": "LG Twins", "inference_inputs": {"away_id": "DOOSAN", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DOOSAN": 1523.924017, "LG": 1506.794811}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "LG", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.283322+00:00", "outcome_probabilities": {"away": 0.484648703228405, "draw": 0.02262693, "home": 0.492724366771595}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.495962, "home": 0.504038}, "snapshot_hash": "cf1df3745177e4ea6b73c766e3bd90118f6d77b3d5d0fa9466d332ae291e5a03", "sport": "KBO"}</t>
+          <t>{"artifact_hash": "72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a", "away_team": "Doosan Bears", "draw_settlement_value": 0.5, "event_id": "141707", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1523.924017, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1506.794811}, "historical_source_observation_times_verified": false, "home_team": "LG Twins", "inference_inputs": {"away_id": "DOOSAN", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DOOSAN": 1523.924017, "LG": 1506.794811}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "58ea522476e21dc70a719fe60647c19a772fcb4703fef8ed2d47c4ba7f07c2d5"}, "home_id": "LG", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-07T05:28:32.629666+00:00", "outcome_probabilities": {"away": 0.484648703228405, "draw": 0.02262693, "home": 0.492724366771595}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.495962, "home": 0.504038}, "snapshot_hash": "afd033d4d28b8c64adf094a239b2036217e1f5a181bc3d411f635dc9a4692ef9", "sport": "KBO"}</t>
         </is>
       </c>
     </row>
     <row r="165" ht="36" customHeight="1">
       <c r="A165" s="24" t="inlineStr">
         <is>
-          <t>eeac7360664c4a91</t>
+          <t>ea7c1efe6a114554</t>
         </is>
       </c>
       <c r="B165" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:10.987601Z</t>
+          <t>2026-10-07T05:28:43.252505Z</t>
         </is>
       </c>
       <c r="C165" s="24" t="inlineStr">
@@ -53057,23 +53105,23 @@
         </is>
       </c>
       <c r="L165" s="26" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="M165" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.961538</v>
       </c>
       <c r="N165" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.509804</v>
       </c>
       <c r="O165" s="28" t="n">
         <v>0.577223</v>
       </c>
       <c r="P165" s="28" t="n"/>
       <c r="Q165" s="28" t="n">
-        <v>0.057992</v>
+        <v>0.06741900000000001</v>
       </c>
       <c r="R165" s="26" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="S165" s="29" t="n">
         <v>1</v>
@@ -53085,21 +53133,41 @@
       </c>
       <c r="U165" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V165" s="24" t="n"/>
-      <c r="W165" s="26" t="n"/>
-      <c r="X165" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V165" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W165" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X165" s="26" t="n">
+        <v>9</v>
+      </c>
       <c r="Y165" s="25" t="n"/>
-      <c r="Z165" s="26" t="n"/>
-      <c r="AA165" s="28" t="n"/>
-      <c r="AB165" s="28" t="n"/>
-      <c r="AC165" s="30" t="n"/>
-      <c r="AD165" s="24" t="n"/>
+      <c r="Z165" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="AA165" s="28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB165" s="28" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="AC165" s="30" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="AD165" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:04:53.100098Z</t>
+        </is>
+      </c>
       <c r="AE165" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.5200 (market_slug=aec-kbo-kwt-sla-2026-10-07). Tie probability=0.0226.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.5100 (market_slug=aec-kbo-kwt-sla-2026-10-07). Tie probability=0.0226.</t>
         </is>
       </c>
       <c r="AF165" s="31" t="inlineStr">
@@ -53183,7 +53251,7 @@
       </c>
       <c r="BA165" s="24" t="inlineStr">
         <is>
-          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+          <t>72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a</t>
         </is>
       </c>
       <c r="BB165" s="24" t="inlineStr">
@@ -53198,7 +53266,7 @@
       </c>
       <c r="BD165" s="24" t="inlineStr">
         <is>
-          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+          <t>72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a</t>
         </is>
       </c>
       <c r="BE165" s="24" t="inlineStr">
@@ -53218,7 +53286,7 @@
       </c>
       <c r="BH165" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:24:50.489684Z</t>
+          <t>2026-10-07T05:28:32.894290Z</t>
         </is>
       </c>
       <c r="BI165" s="24" t="inlineStr">
@@ -53228,19 +53296,23 @@
       </c>
       <c r="BJ165" s="25" t="n"/>
       <c r="BK165" s="26" t="n">
-        <v>-108</v>
+        <v>-104</v>
       </c>
       <c r="BL165" s="27" t="n">
-        <v>1.925926</v>
+        <v>1.961538</v>
       </c>
       <c r="BM165" s="28" t="n">
-        <v>0.519231</v>
+        <v>0.509804</v>
       </c>
       <c r="BN165" s="28" t="n"/>
       <c r="BO165" s="28" t="n"/>
       <c r="BP165" s="25" t="n"/>
-      <c r="BQ165" s="27" t="n"/>
-      <c r="BR165" s="28" t="n"/>
+      <c r="BQ165" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BR165" s="28" t="n">
+        <v>0.51</v>
+      </c>
       <c r="BS165" s="28" t="n"/>
       <c r="BT165" s="28" t="n"/>
       <c r="BU165" s="25" t="n"/>
@@ -53297,19 +53369,19 @@
       <c r="DP165" s="24" t="n"/>
       <c r="DQ165" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114", "away_team": "Samsung Lions", "draw_settlement_value": 0.5, "event_id": "141708", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1543.670103, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1579.036662}, "historical_source_observation_times_verified": false, "home_team": "KT Wiz", "inference_inputs": {"away_id": "SAMSUNG", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"KT": 1579.036662, "SAMSUNG": 1543.670103}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "KT", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.283322+00:00", "outcome_probabilities": {"away": 0.4114631296070524, "draw": 0.02262693, "home": 0.5659099403929476}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.422777, "home": 0.577223}, "snapshot_hash": "3fae4502ed3b14dbbf2cf166b4d67390c55d456648b342cdafced37495eacc0f", "sport": "KBO"}</t>
+          <t>{"artifact_hash": "72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a", "away_team": "Samsung Lions", "draw_settlement_value": 0.5, "event_id": "141708", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1543.670103, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1579.036662}, "historical_source_observation_times_verified": false, "home_team": "KT Wiz", "inference_inputs": {"away_id": "SAMSUNG", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"KT": 1579.036662, "SAMSUNG": 1543.670103}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "58ea522476e21dc70a719fe60647c19a772fcb4703fef8ed2d47c4ba7f07c2d5"}, "home_id": "KT", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-07T05:28:32.629666+00:00", "outcome_probabilities": {"away": 0.4114631296070524, "draw": 0.02262693, "home": 0.5659099403929476}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.422777, "home": 0.577223}, "snapshot_hash": "d31379a8820d834cabbc3ee9cc08c7cb47f5e4af35d62037620e3185bc3ed430", "sport": "KBO"}</t>
         </is>
       </c>
     </row>
     <row r="166" ht="36" customHeight="1">
       <c r="A166" s="24" t="inlineStr">
         <is>
-          <t>fc1d0965db9e40ef</t>
+          <t>e02528caf207470e</t>
         </is>
       </c>
       <c r="B166" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:10.987601Z</t>
+          <t>2026-10-07T05:28:43.252505Z</t>
         </is>
       </c>
       <c r="C166" s="24" t="inlineStr">
@@ -53354,20 +53426,20 @@
         </is>
       </c>
       <c r="L166" s="26" t="n">
-        <v>-163</v>
+        <v>-186</v>
       </c>
       <c r="M166" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.537634</v>
       </c>
       <c r="N166" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.65035</v>
       </c>
       <c r="O166" s="28" t="n">
         <v>0.5302480000000001</v>
       </c>
       <c r="P166" s="28" t="n"/>
       <c r="Q166" s="28" t="n">
-        <v>-0.08952400000000001</v>
+        <v>-0.120102</v>
       </c>
       <c r="R166" s="26" t="n">
         <v>0</v>
@@ -53382,21 +53454,41 @@
       </c>
       <c r="U166" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V166" s="24" t="n"/>
-      <c r="W166" s="26" t="n"/>
-      <c r="X166" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V166" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W166" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="X166" s="26" t="n">
+        <v>4</v>
+      </c>
       <c r="Y166" s="25" t="n"/>
-      <c r="Z166" s="26" t="n"/>
-      <c r="AA166" s="28" t="n"/>
-      <c r="AB166" s="28" t="n"/>
-      <c r="AC166" s="30" t="n"/>
-      <c r="AD166" s="24" t="n"/>
+      <c r="Z166" s="26" t="n">
+        <v>-186</v>
+      </c>
+      <c r="AA166" s="28" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="AB166" s="28" t="n">
+        <v>-0.00035</v>
+      </c>
+      <c r="AC166" s="30" t="n">
+        <v>0.5376</v>
+      </c>
+      <c r="AD166" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:04:54.249745Z</t>
+        </is>
+      </c>
       <c r="AE166" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.6200 (market_slug=aec-kbo-lgo-kti-2026-10-07). Tie probability=0.0226.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.6500 (market_slug=aec-kbo-lgo-kti-2026-10-07). Tie probability=0.0226.</t>
         </is>
       </c>
       <c r="AF166" s="31" t="inlineStr">
@@ -53480,7 +53572,7 @@
       </c>
       <c r="BA166" s="24" t="inlineStr">
         <is>
-          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+          <t>72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a</t>
         </is>
       </c>
       <c r="BB166" s="24" t="inlineStr">
@@ -53495,7 +53587,7 @@
       </c>
       <c r="BD166" s="24" t="inlineStr">
         <is>
-          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+          <t>72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a</t>
         </is>
       </c>
       <c r="BE166" s="24" t="inlineStr">
@@ -53515,7 +53607,7 @@
       </c>
       <c r="BH166" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:24:50.570264Z</t>
+          <t>2026-10-07T05:28:32.949702Z</t>
         </is>
       </c>
       <c r="BI166" s="24" t="inlineStr">
@@ -53525,19 +53617,23 @@
       </c>
       <c r="BJ166" s="25" t="n"/>
       <c r="BK166" s="26" t="n">
-        <v>-163</v>
+        <v>-186</v>
       </c>
       <c r="BL166" s="27" t="n">
-        <v>1.613497</v>
+        <v>1.537634</v>
       </c>
       <c r="BM166" s="28" t="n">
-        <v>0.619772</v>
+        <v>0.65035</v>
       </c>
       <c r="BN166" s="28" t="n"/>
       <c r="BO166" s="28" t="n"/>
       <c r="BP166" s="25" t="n"/>
-      <c r="BQ166" s="27" t="n"/>
-      <c r="BR166" s="28" t="n"/>
+      <c r="BQ166" s="27" t="n">
+        <v>1.537634</v>
+      </c>
+      <c r="BR166" s="28" t="n">
+        <v>0.65</v>
+      </c>
       <c r="BS166" s="28" t="n"/>
       <c r="BT166" s="28" t="n"/>
       <c r="BU166" s="25" t="n"/>
@@ -53594,19 +53690,19 @@
       <c r="DP166" s="24" t="n"/>
       <c r="DQ166" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114", "away_team": "Kia Tigers", "draw_settlement_value": 0.5, "event_id": "141709", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1524.366838, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1482.834576}, "historical_source_observation_times_verified": false, "home_team": "Lotte Giants", "inference_inputs": {"away_id": "KIA", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"KIA": 1524.366838, "LOTTE": 1482.834576}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "LOTTE", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.283322+00:00", "outcome_probabilities": {"away": 0.5189340850239297, "draw": 0.02262693, "home": 0.4584389849760702}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.530248, "home": 0.469752}, "snapshot_hash": "7224fd777d486ed64d33b68c30084e68ac7193ae5a6ee397c4e0e18c916f3b21", "sport": "KBO"}</t>
+          <t>{"artifact_hash": "72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a", "away_team": "Kia Tigers", "draw_settlement_value": 0.5, "event_id": "141709", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1524.366838, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1482.834576}, "historical_source_observation_times_verified": false, "home_team": "Lotte Giants", "inference_inputs": {"away_id": "KIA", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"KIA": 1524.366838, "LOTTE": 1482.834576}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "58ea522476e21dc70a719fe60647c19a772fcb4703fef8ed2d47c4ba7f07c2d5"}, "home_id": "LOTTE", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-07T05:28:32.629666+00:00", "outcome_probabilities": {"away": 0.5189340850239297, "draw": 0.02262693, "home": 0.4584389849760702}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.530248, "home": 0.469752}, "snapshot_hash": "048e2961bfb8400774b98a93c17330cd95e94c3aa95b43edaf021a161f941186", "sport": "KBO"}</t>
         </is>
       </c>
     </row>
     <row r="167" ht="36" customHeight="1">
       <c r="A167" s="24" t="inlineStr">
         <is>
-          <t>45135b7cf1c746d1</t>
+          <t>4f8dcf8f72aa4c76</t>
         </is>
       </c>
       <c r="B167" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:10.987601Z</t>
+          <t>2026-10-07T05:28:43.252505Z</t>
         </is>
       </c>
       <c r="C167" s="24" t="inlineStr">
@@ -53679,18 +53775,38 @@
       </c>
       <c r="U167" s="24" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="V167" s="24" t="n"/>
-      <c r="W167" s="26" t="n"/>
-      <c r="X167" s="26" t="n"/>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V167" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W167" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="X167" s="26" t="n">
+        <v>5</v>
+      </c>
       <c r="Y167" s="25" t="n"/>
-      <c r="Z167" s="26" t="n"/>
-      <c r="AA167" s="28" t="n"/>
-      <c r="AB167" s="28" t="n"/>
-      <c r="AC167" s="30" t="n"/>
-      <c r="AD167" s="24" t="n"/>
+      <c r="Z167" s="26" t="n">
+        <v>144</v>
+      </c>
+      <c r="AA167" s="28" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB167" s="28" t="n">
+        <v>0.000164</v>
+      </c>
+      <c r="AC167" s="30" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AD167" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-07T16:04:55.563956Z</t>
+        </is>
+      </c>
       <c r="AE167" s="31" t="inlineStr">
         <is>
           <t>Tie-aware Elo baseline; executable ask 0.4100 (market_slug=aec-kbo-khi-hea-2026-10-07). Tie probability=0.0226.</t>
@@ -53777,7 +53893,7 @@
       </c>
       <c r="BA167" s="24" t="inlineStr">
         <is>
-          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+          <t>72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a</t>
         </is>
       </c>
       <c r="BB167" s="24" t="inlineStr">
@@ -53792,7 +53908,7 @@
       </c>
       <c r="BD167" s="24" t="inlineStr">
         <is>
-          <t>7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114</t>
+          <t>72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a</t>
         </is>
       </c>
       <c r="BE167" s="24" t="inlineStr">
@@ -53812,7 +53928,7 @@
       </c>
       <c r="BH167" s="24" t="inlineStr">
         <is>
-          <t>2026-10-06T22:25:10.987601Z</t>
+          <t>2026-10-07T05:28:43.252505Z</t>
         </is>
       </c>
       <c r="BI167" s="24" t="inlineStr">
@@ -53833,8 +53949,12 @@
       <c r="BN167" s="28" t="n"/>
       <c r="BO167" s="28" t="n"/>
       <c r="BP167" s="25" t="n"/>
-      <c r="BQ167" s="27" t="n"/>
-      <c r="BR167" s="28" t="n"/>
+      <c r="BQ167" s="27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BR167" s="28" t="n">
+        <v>0.41</v>
+      </c>
       <c r="BS167" s="28" t="n"/>
       <c r="BT167" s="28" t="n"/>
       <c r="BU167" s="25" t="n"/>
@@ -53891,7 +54011,1889 @@
       <c r="DP167" s="24" t="n"/>
       <c r="DQ167" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "7cff2807fc660517fbda95f730a6a901b570d0845019c5e524dde23a826f7114", "away_team": "Hanwha Eagles", "draw_settlement_value": 0.5, "event_id": "141710", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1438.436026, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1440.024074}, "historical_source_observation_times_verified": false, "home_team": "Kiwoom Heroes", "inference_inputs": {"away_id": "HANWHA", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"HANWHA": 1438.436026, "KIWOOM": 1440.024074}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "f345eb917316d2e897f62c1cdd0f73153115c65da54c30c6137ad76bb7b27869"}, "home_id": "KIWOOM", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-06T22:24:50.283322+00:00", "outcome_probabilities": {"away": 0.45836082040103526, "draw": 0.02262693, "home": 0.5190122495989647}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.469674, "home": 0.530326}, "snapshot_hash": "322b7cf15492d4f871004a8d048c4176fc52dec89f029ce76c72682e2d17a07b", "sport": "KBO"}</t>
+          <t>{"artifact_hash": "72d934bf14f15b6340db5d573213dae372bfc880b7d95295d2b9d3795bdd3a0a", "away_team": "Hanwha Eagles", "draw_settlement_value": 0.5, "event_id": "141710", "event_start_utc": "2026-10-07T09:30:00Z", "features": {"away_elo": 1438.436026, "base_tie_rate": 0.02262693, "home_advantage": 20.0, "home_elo": 1440.024074}, "historical_source_observation_times_verified": false, "home_team": "Kiwoom Heroes", "inference_inputs": {"away_id": "HANWHA", "base_tie_rate": 0.02262693, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"HANWHA": 1438.436026, "KIWOOM": 1440.024074}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "58ea522476e21dc70a719fe60647c19a772fcb4703fef8ed2d47c4ba7f07c2d5"}, "home_id": "KIWOOM", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-07T05:28:32.629666+00:00", "outcome_probabilities": {"away": 0.45836082040103526, "draw": 0.02262693, "home": 0.5190122495989647}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.469674, "home": 0.530326}, "snapshot_hash": "907388d3fdba88097c0528b56a903f4aaac0dc5a91b17d6048a51098a120d5aa", "sport": "KBO"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="36" customHeight="1">
+      <c r="A168" s="24" t="inlineStr">
+        <is>
+          <t>ae97d9314e5c46e9</t>
+        </is>
+      </c>
+      <c r="B168" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:06:46.442216Z</t>
+        </is>
+      </c>
+      <c r="C168" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D168" s="24" t="inlineStr">
+        <is>
+          <t>148641</t>
+        </is>
+      </c>
+      <c r="E168" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F168" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="G168" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="H168" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I168" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J168" s="25" t="n"/>
+      <c r="K168" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L168" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="M168" s="27" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="N168" s="28" t="n">
+        <v>0.760192</v>
+      </c>
+      <c r="O168" s="28" t="n">
+        <v>0.604778</v>
+      </c>
+      <c r="P168" s="28" t="n"/>
+      <c r="Q168" s="28" t="n">
+        <v>-0.155414</v>
+      </c>
+      <c r="R168" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S168" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T168" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U168" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V168" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W168" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X168" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y168" s="25" t="n"/>
+      <c r="Z168" s="26" t="n"/>
+      <c r="AA168" s="28" t="n"/>
+      <c r="AB168" s="28" t="n"/>
+      <c r="AC168" s="30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AD168" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T10:03:33.225577Z</t>
+        </is>
+      </c>
+      <c r="AE168" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.7600 (market_slug=aec-kbo-kti-lgo-2026-10-11). Tie probability=0.0226.</t>
+        </is>
+      </c>
+      <c r="AF168" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG168" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH168" s="24" t="n"/>
+      <c r="AI168" s="31" t="n"/>
+      <c r="AJ168" s="31" t="n"/>
+      <c r="AK168" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL168" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM168" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN168" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO168" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP168" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AQ168" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AR168" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AS168" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AT168" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AU168" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AV168" s="24" t="n"/>
+      <c r="AW168" s="24" t="n"/>
+      <c r="AX168" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY168" s="24" t="n"/>
+      <c r="AZ168" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA168" s="24" t="inlineStr">
+        <is>
+          <t>341c7e2b0ea30be66dd305c47452d403a5fa249e98491a2f79156a336a3015bb</t>
+        </is>
+      </c>
+      <c r="BB168" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC168" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD168" s="24" t="inlineStr">
+        <is>
+          <t>341c7e2b0ea30be66dd305c47452d403a5fa249e98491a2f79156a336a3015bb</t>
+        </is>
+      </c>
+      <c r="BE168" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF168" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG168" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH168" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:06:46.388523Z</t>
+        </is>
+      </c>
+      <c r="BI168" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ168" s="25" t="n"/>
+      <c r="BK168" s="26" t="n">
+        <v>-317</v>
+      </c>
+      <c r="BL168" s="27" t="n">
+        <v>1.315457</v>
+      </c>
+      <c r="BM168" s="28" t="n">
+        <v>0.760192</v>
+      </c>
+      <c r="BN168" s="28" t="n"/>
+      <c r="BO168" s="28" t="n"/>
+      <c r="BP168" s="25" t="n"/>
+      <c r="BQ168" s="27" t="n"/>
+      <c r="BR168" s="28" t="n"/>
+      <c r="BS168" s="28" t="n"/>
+      <c r="BT168" s="28" t="n"/>
+      <c r="BU168" s="25" t="n"/>
+      <c r="BV168" s="29" t="n"/>
+      <c r="BW168" s="24" t="n"/>
+      <c r="BX168" s="30" t="n"/>
+      <c r="BY168" s="27" t="n"/>
+      <c r="BZ168" s="24" t="n"/>
+      <c r="CA168" s="31" t="n"/>
+      <c r="CB168" s="24" t="n"/>
+      <c r="CC168" s="24" t="n"/>
+      <c r="CD168" s="24" t="n"/>
+      <c r="CE168" s="24" t="n"/>
+      <c r="CF168" s="24" t="n"/>
+      <c r="CG168" s="24" t="n"/>
+      <c r="CH168" s="24" t="n"/>
+      <c r="CI168" s="24" t="n"/>
+      <c r="CJ168" s="24" t="n"/>
+      <c r="CK168" s="24" t="n"/>
+      <c r="CL168" s="24" t="n"/>
+      <c r="CM168" s="24" t="n"/>
+      <c r="CN168" s="24" t="n"/>
+      <c r="CO168" s="24" t="n"/>
+      <c r="CP168" s="24" t="n"/>
+      <c r="CQ168" s="24" t="n"/>
+      <c r="CR168" s="24" t="n"/>
+      <c r="CS168" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT168" s="24" t="n"/>
+      <c r="CU168" s="24" t="n"/>
+      <c r="CV168" s="24" t="n"/>
+      <c r="CW168" s="24" t="n"/>
+      <c r="CX168" s="24" t="n"/>
+      <c r="CY168" s="24" t="n"/>
+      <c r="CZ168" s="24" t="n"/>
+      <c r="DA168" s="24" t="n"/>
+      <c r="DB168" s="24" t="n"/>
+      <c r="DC168" s="24" t="n"/>
+      <c r="DD168" s="24" t="n"/>
+      <c r="DE168" s="24" t="n"/>
+      <c r="DF168" s="24" t="n"/>
+      <c r="DG168" s="24" t="n"/>
+      <c r="DH168" s="24" t="n"/>
+      <c r="DI168" s="24" t="n"/>
+      <c r="DJ168" s="24" t="n"/>
+      <c r="DK168" s="24" t="n"/>
+      <c r="DL168" s="24" t="n"/>
+      <c r="DM168" s="24" t="n"/>
+      <c r="DN168" s="24" t="n"/>
+      <c r="DO168" s="24" t="n"/>
+      <c r="DP168" s="24" t="n"/>
+      <c r="DQ168" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "341c7e2b0ea30be66dd305c47452d403a5fa249e98491a2f79156a336a3015bb", "away_team": "Lotte Giants", "draw_settlement_value": 0.5, "event_id": "148641", "event_start_utc": "2026-10-11T05:00:00Z", "features": {"away_elo": 1479.387378, "base_tie_rate": 0.02259264, "home_advantage": 20.0, "home_elo": 1535.051436}, "historical_source_observation_times_verified": false, "home_team": "Kia Tigers", "inference_inputs": {"away_id": "LOTTE", "base_tie_rate": 0.02259264, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"KIA": 1535.051436, "LOTTE": 1479.387378}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "KIA", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-11T01:06:46.324600+00:00", "outcome_probabilities": {"away": 0.3839256854980043, "draw": 0.02259264, "home": 0.5934816745019956}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.395222, "home": 0.604778}, "snapshot_hash": "93d5a7b26981d45a45f7121e46f9bc0accb1d8404bcafa61f4e38d5b72595fb1", "sport": "KBO"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="36" customHeight="1">
+      <c r="A169" s="24" t="inlineStr">
+        <is>
+          <t>e0710678d8d2467e</t>
+        </is>
+      </c>
+      <c r="B169" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:06:46.442216Z</t>
+        </is>
+      </c>
+      <c r="C169" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T05:00:00Z</t>
+        </is>
+      </c>
+      <c r="D169" s="24" t="inlineStr">
+        <is>
+          <t>148642</t>
+        </is>
+      </c>
+      <c r="E169" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F169" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="G169" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="H169" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I169" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J169" s="25" t="n"/>
+      <c r="K169" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L169" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="M169" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="N169" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="O169" s="28" t="n">
+        <v>0.5353</v>
+      </c>
+      <c r="P169" s="28" t="n"/>
+      <c r="Q169" s="28" t="n">
+        <v>-0.003871</v>
+      </c>
+      <c r="R169" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="S169" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T169" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U169" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V169" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W169" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="X169" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y169" s="25" t="n"/>
+      <c r="Z169" s="26" t="n"/>
+      <c r="AA169" s="28" t="n"/>
+      <c r="AB169" s="28" t="n"/>
+      <c r="AC169" s="30" t="n">
+        <v>0.8547</v>
+      </c>
+      <c r="AD169" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T10:03:34.972588Z</t>
+        </is>
+      </c>
+      <c r="AE169" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5400 (market_slug=aec-kbo-sla-kwt-2026-10-11). Tie probability=0.0226.</t>
+        </is>
+      </c>
+      <c r="AF169" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG169" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH169" s="24" t="n"/>
+      <c r="AI169" s="31" t="n"/>
+      <c r="AJ169" s="31" t="n"/>
+      <c r="AK169" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL169" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM169" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN169" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO169" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP169" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AQ169" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AR169" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AS169" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AT169" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AU169" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AV169" s="24" t="n"/>
+      <c r="AW169" s="24" t="n"/>
+      <c r="AX169" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY169" s="24" t="n"/>
+      <c r="AZ169" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA169" s="24" t="inlineStr">
+        <is>
+          <t>341c7e2b0ea30be66dd305c47452d403a5fa249e98491a2f79156a336a3015bb</t>
+        </is>
+      </c>
+      <c r="BB169" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC169" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD169" s="24" t="inlineStr">
+        <is>
+          <t>341c7e2b0ea30be66dd305c47452d403a5fa249e98491a2f79156a336a3015bb</t>
+        </is>
+      </c>
+      <c r="BE169" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF169" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG169" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH169" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-11T01:06:46.442216Z</t>
+        </is>
+      </c>
+      <c r="BI169" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ169" s="25" t="n"/>
+      <c r="BK169" s="26" t="n">
+        <v>-117</v>
+      </c>
+      <c r="BL169" s="27" t="n">
+        <v>1.854701</v>
+      </c>
+      <c r="BM169" s="28" t="n">
+        <v>0.539171</v>
+      </c>
+      <c r="BN169" s="28" t="n"/>
+      <c r="BO169" s="28" t="n"/>
+      <c r="BP169" s="25" t="n"/>
+      <c r="BQ169" s="27" t="n"/>
+      <c r="BR169" s="28" t="n"/>
+      <c r="BS169" s="28" t="n"/>
+      <c r="BT169" s="28" t="n"/>
+      <c r="BU169" s="25" t="n"/>
+      <c r="BV169" s="29" t="n"/>
+      <c r="BW169" s="24" t="n"/>
+      <c r="BX169" s="30" t="n"/>
+      <c r="BY169" s="27" t="n"/>
+      <c r="BZ169" s="24" t="n"/>
+      <c r="CA169" s="31" t="n"/>
+      <c r="CB169" s="24" t="n"/>
+      <c r="CC169" s="24" t="n"/>
+      <c r="CD169" s="24" t="n"/>
+      <c r="CE169" s="24" t="n"/>
+      <c r="CF169" s="24" t="n"/>
+      <c r="CG169" s="24" t="n"/>
+      <c r="CH169" s="24" t="n"/>
+      <c r="CI169" s="24" t="n"/>
+      <c r="CJ169" s="24" t="n"/>
+      <c r="CK169" s="24" t="n"/>
+      <c r="CL169" s="24" t="n"/>
+      <c r="CM169" s="24" t="n"/>
+      <c r="CN169" s="24" t="n"/>
+      <c r="CO169" s="24" t="n"/>
+      <c r="CP169" s="24" t="n"/>
+      <c r="CQ169" s="24" t="n"/>
+      <c r="CR169" s="24" t="n"/>
+      <c r="CS169" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT169" s="24" t="n"/>
+      <c r="CU169" s="24" t="n"/>
+      <c r="CV169" s="24" t="n"/>
+      <c r="CW169" s="24" t="n"/>
+      <c r="CX169" s="24" t="n"/>
+      <c r="CY169" s="24" t="n"/>
+      <c r="CZ169" s="24" t="n"/>
+      <c r="DA169" s="24" t="n"/>
+      <c r="DB169" s="24" t="n"/>
+      <c r="DC169" s="24" t="n"/>
+      <c r="DD169" s="24" t="n"/>
+      <c r="DE169" s="24" t="n"/>
+      <c r="DF169" s="24" t="n"/>
+      <c r="DG169" s="24" t="n"/>
+      <c r="DH169" s="24" t="n"/>
+      <c r="DI169" s="24" t="n"/>
+      <c r="DJ169" s="24" t="n"/>
+      <c r="DK169" s="24" t="n"/>
+      <c r="DL169" s="24" t="n"/>
+      <c r="DM169" s="24" t="n"/>
+      <c r="DN169" s="24" t="n"/>
+      <c r="DO169" s="24" t="n"/>
+      <c r="DP169" s="24" t="n"/>
+      <c r="DQ169" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "341c7e2b0ea30be66dd305c47452d403a5fa249e98491a2f79156a336a3015bb", "away_team": "KT Wiz", "draw_settlement_value": 0.5, "event_id": "148642", "event_start_utc": "2026-10-11T05:00:00Z", "features": {"away_elo": 1580.7886, "base_tie_rate": 0.02259264, "home_advantage": 20.0, "home_elo": 1535.648797}, "historical_source_observation_times_verified": false, "home_team": "Samsung Lions", "inference_inputs": {"away_id": "KT", "base_tie_rate": 0.02259264, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"KT": 1580.7886, "SAMSUNG": 1535.648797}}, "code_sha256": {"features/elo_ratings.py": "8525faf022a6343c452286dbfeb17dbb043744c6bdabbe448b6b371216da439b", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "SAMSUNG", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-11T01:06:46.324600+00:00", "outcome_probabilities": {"away": 0.5240037982249255, "draw": 0.02259264, "home": 0.4534035617750744}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.5353, "home": 0.4647}, "snapshot_hash": "2ac60c4611042d75927eb8c2a2eb75a1dd1836a3e7d286efcf4a0e513d858a37", "sport": "KBO"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="36" customHeight="1">
+      <c r="A170" s="24" t="inlineStr">
+        <is>
+          <t>85e9275c300443df</t>
+        </is>
+      </c>
+      <c r="B170" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T05:39:17.217038Z</t>
+        </is>
+      </c>
+      <c r="C170" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D170" s="24" t="inlineStr">
+        <is>
+          <t>150824</t>
+        </is>
+      </c>
+      <c r="E170" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F170" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="G170" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="H170" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I170" s="24" t="inlineStr">
+        <is>
+          <t>away</t>
+        </is>
+      </c>
+      <c r="J170" s="25" t="n"/>
+      <c r="K170" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L170" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="M170" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="N170" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="O170" s="28" t="n">
+        <v>0.545318</v>
+      </c>
+      <c r="P170" s="28" t="n"/>
+      <c r="Q170" s="28" t="n">
+        <v>-0.09497</v>
+      </c>
+      <c r="R170" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S170" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T170" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U170" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V170" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W170" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="X170" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y170" s="25" t="n"/>
+      <c r="Z170" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="AA170" s="28" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AB170" s="28" t="n">
+        <v>-0.000288</v>
+      </c>
+      <c r="AC170" s="30" t="n">
+        <v>0.5618</v>
+      </c>
+      <c r="AD170" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T16:15:02.035490Z</t>
+        </is>
+      </c>
+      <c r="AE170" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.6400 (market_slug=aec-kbo-sla-kwt-2026-10-12). Tie probability=0.0226.</t>
+        </is>
+      </c>
+      <c r="AF170" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG170" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH170" s="24" t="n"/>
+      <c r="AI170" s="31" t="n"/>
+      <c r="AJ170" s="31" t="n"/>
+      <c r="AK170" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL170" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM170" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN170" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO170" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP170" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AQ170" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AR170" s="24" t="inlineStr">
+        <is>
+          <t>KT Wiz</t>
+        </is>
+      </c>
+      <c r="AS170" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AT170" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AU170" s="24" t="inlineStr">
+        <is>
+          <t>Samsung Lions</t>
+        </is>
+      </c>
+      <c r="AV170" s="24" t="n"/>
+      <c r="AW170" s="24" t="n"/>
+      <c r="AX170" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY170" s="24" t="n"/>
+      <c r="AZ170" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA170" s="24" t="inlineStr">
+        <is>
+          <t>f828956be898ea82909cc2c95471f23915163bd39f9e25da1a377dad461ebb9b</t>
+        </is>
+      </c>
+      <c r="BB170" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC170" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD170" s="24" t="inlineStr">
+        <is>
+          <t>f828956be898ea82909cc2c95471f23915163bd39f9e25da1a377dad461ebb9b</t>
+        </is>
+      </c>
+      <c r="BE170" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF170" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG170" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH170" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T05:39:17.051665Z</t>
+        </is>
+      </c>
+      <c r="BI170" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ170" s="25" t="n"/>
+      <c r="BK170" s="26" t="n">
+        <v>-178</v>
+      </c>
+      <c r="BL170" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BM170" s="28" t="n">
+        <v>0.640288</v>
+      </c>
+      <c r="BN170" s="28" t="n"/>
+      <c r="BO170" s="28" t="n"/>
+      <c r="BP170" s="25" t="n"/>
+      <c r="BQ170" s="27" t="n">
+        <v>1.561798</v>
+      </c>
+      <c r="BR170" s="28" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BS170" s="28" t="n"/>
+      <c r="BT170" s="28" t="n"/>
+      <c r="BU170" s="25" t="n"/>
+      <c r="BV170" s="29" t="n"/>
+      <c r="BW170" s="24" t="n"/>
+      <c r="BX170" s="30" t="n"/>
+      <c r="BY170" s="27" t="n"/>
+      <c r="BZ170" s="24" t="n"/>
+      <c r="CA170" s="31" t="n"/>
+      <c r="CB170" s="24" t="n"/>
+      <c r="CC170" s="24" t="n"/>
+      <c r="CD170" s="24" t="n"/>
+      <c r="CE170" s="24" t="n"/>
+      <c r="CF170" s="24" t="n"/>
+      <c r="CG170" s="24" t="n"/>
+      <c r="CH170" s="24" t="n"/>
+      <c r="CI170" s="24" t="n"/>
+      <c r="CJ170" s="24" t="n"/>
+      <c r="CK170" s="24" t="n"/>
+      <c r="CL170" s="24" t="n"/>
+      <c r="CM170" s="24" t="n"/>
+      <c r="CN170" s="24" t="n"/>
+      <c r="CO170" s="24" t="n"/>
+      <c r="CP170" s="24" t="n"/>
+      <c r="CQ170" s="24" t="n"/>
+      <c r="CR170" s="24" t="n"/>
+      <c r="CS170" s="24" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="CT170" s="24" t="n"/>
+      <c r="CU170" s="24" t="n"/>
+      <c r="CV170" s="24" t="n"/>
+      <c r="CW170" s="24" t="n"/>
+      <c r="CX170" s="24" t="n"/>
+      <c r="CY170" s="24" t="n"/>
+      <c r="CZ170" s="24" t="n"/>
+      <c r="DA170" s="24" t="n"/>
+      <c r="DB170" s="24" t="n"/>
+      <c r="DC170" s="24" t="n"/>
+      <c r="DD170" s="24" t="n"/>
+      <c r="DE170" s="24" t="n"/>
+      <c r="DF170" s="24" t="n"/>
+      <c r="DG170" s="24" t="n"/>
+      <c r="DH170" s="24" t="n"/>
+      <c r="DI170" s="24" t="n"/>
+      <c r="DJ170" s="24" t="n"/>
+      <c r="DK170" s="24" t="n"/>
+      <c r="DL170" s="24" t="n"/>
+      <c r="DM170" s="24" t="n"/>
+      <c r="DN170" s="24" t="n"/>
+      <c r="DO170" s="24" t="n"/>
+      <c r="DP170" s="24" t="n"/>
+      <c r="DQ170" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "f828956be898ea82909cc2c95471f23915163bd39f9e25da1a377dad461ebb9b", "away_team": "KT Wiz", "draw_settlement_value": 0.5, "event_id": "150824", "event_start_utc": "2026-10-12T09:30:00Z", "features": {"away_elo": 1584.177002, "base_tie_rate": 0.02258642, "home_advantage": 20.0, "home_elo": 1531.866464}, "historical_source_observation_times_verified": false, "home_team": "Samsung Lions", "inference_inputs": {"away_id": "KT", "base_tie_rate": 0.02258642, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"KT": 1584.177002, "SAMSUNG": 1531.866464}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "SAMSUNG", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-12T05:39:16.914450+00:00", "outcome_probabilities": {"away": 0.5340245869223879, "draw": 0.02258642, "home": 0.4433889930776122}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.545318, "home": 0.454682}, "snapshot_hash": "414f5b656cf89e6e627a764df1550d638c17439ddebd33e82e621ef327a6e6ed", "sport": "KBO"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="36" customHeight="1">
+      <c r="A171" s="24" t="inlineStr">
+        <is>
+          <t>bc42c50eefde4257</t>
+        </is>
+      </c>
+      <c r="B171" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T05:39:17.217038Z</t>
+        </is>
+      </c>
+      <c r="C171" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D171" s="24" t="inlineStr">
+        <is>
+          <t>150825</t>
+        </is>
+      </c>
+      <c r="E171" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F171" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="G171" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="H171" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I171" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J171" s="25" t="n"/>
+      <c r="K171" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L171" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="M171" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="N171" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="O171" s="28" t="n">
+        <v>0.576893</v>
+      </c>
+      <c r="P171" s="28" t="n"/>
+      <c r="Q171" s="28" t="n">
+        <v>0.116064</v>
+      </c>
+      <c r="R171" s="26" t="n">
+        <v>78</v>
+      </c>
+      <c r="S171" s="29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T171" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U171" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V171" s="24" t="inlineStr">
+        <is>
+          <t>loss</t>
+        </is>
+      </c>
+      <c r="W171" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="X171" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y171" s="25" t="n"/>
+      <c r="Z171" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="AA171" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AB171" s="28" t="n">
+        <v>-0.000829</v>
+      </c>
+      <c r="AC171" s="30" t="n">
+        <v>-1.5</v>
+      </c>
+      <c r="AD171" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T16:15:06.566833Z</t>
+        </is>
+      </c>
+      <c r="AE171" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4600 (market_slug=aec-kbo-dbo-lgo-2026-10-12). Tie probability=0.0226.</t>
+        </is>
+      </c>
+      <c r="AF171" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG171" s="24" t="inlineStr">
+        <is>
+          <t>review_required</t>
+        </is>
+      </c>
+      <c r="AH171" s="24" t="n"/>
+      <c r="AI171" s="31" t="n"/>
+      <c r="AJ171" s="31" t="n"/>
+      <c r="AK171" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL171" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM171" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN171" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO171" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP171" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AQ171" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AR171" s="24" t="inlineStr">
+        <is>
+          <t>Lotte Giants</t>
+        </is>
+      </c>
+      <c r="AS171" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AT171" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AU171" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AV171" s="24" t="n"/>
+      <c r="AW171" s="24" t="n"/>
+      <c r="AX171" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY171" s="24" t="n"/>
+      <c r="AZ171" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA171" s="24" t="inlineStr">
+        <is>
+          <t>f828956be898ea82909cc2c95471f23915163bd39f9e25da1a377dad461ebb9b</t>
+        </is>
+      </c>
+      <c r="BB171" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC171" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD171" s="24" t="inlineStr">
+        <is>
+          <t>f828956be898ea82909cc2c95471f23915163bd39f9e25da1a377dad461ebb9b</t>
+        </is>
+      </c>
+      <c r="BE171" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF171" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG171" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH171" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T05:39:17.127133Z</t>
+        </is>
+      </c>
+      <c r="BI171" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ171" s="25" t="n"/>
+      <c r="BK171" s="26" t="n">
+        <v>117</v>
+      </c>
+      <c r="BL171" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BM171" s="28" t="n">
+        <v>0.460829</v>
+      </c>
+      <c r="BN171" s="28" t="n"/>
+      <c r="BO171" s="28" t="n"/>
+      <c r="BP171" s="25" t="n"/>
+      <c r="BQ171" s="27" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BR171" s="28" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BS171" s="28" t="n"/>
+      <c r="BT171" s="28" t="n"/>
+      <c r="BU171" s="25" t="n"/>
+      <c r="BV171" s="29" t="n"/>
+      <c r="BW171" s="24" t="n"/>
+      <c r="BX171" s="30" t="n"/>
+      <c r="BY171" s="27" t="n"/>
+      <c r="BZ171" s="24" t="n"/>
+      <c r="CA171" s="31" t="n"/>
+      <c r="CB171" s="24" t="n"/>
+      <c r="CC171" s="24" t="n"/>
+      <c r="CD171" s="24" t="n"/>
+      <c r="CE171" s="24" t="n"/>
+      <c r="CF171" s="24" t="n"/>
+      <c r="CG171" s="24" t="n"/>
+      <c r="CH171" s="24" t="n"/>
+      <c r="CI171" s="24" t="n"/>
+      <c r="CJ171" s="24" t="n"/>
+      <c r="CK171" s="24" t="n"/>
+      <c r="CL171" s="24" t="n"/>
+      <c r="CM171" s="24" t="n"/>
+      <c r="CN171" s="24" t="n"/>
+      <c r="CO171" s="24" t="n"/>
+      <c r="CP171" s="24" t="n"/>
+      <c r="CQ171" s="24" t="n"/>
+      <c r="CR171" s="24" t="n"/>
+      <c r="CS171" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT171" s="24" t="n"/>
+      <c r="CU171" s="24" t="n"/>
+      <c r="CV171" s="24" t="n"/>
+      <c r="CW171" s="24" t="n"/>
+      <c r="CX171" s="24" t="n"/>
+      <c r="CY171" s="24" t="n"/>
+      <c r="CZ171" s="24" t="n"/>
+      <c r="DA171" s="24" t="n"/>
+      <c r="DB171" s="24" t="n"/>
+      <c r="DC171" s="24" t="n"/>
+      <c r="DD171" s="24" t="n"/>
+      <c r="DE171" s="24" t="n"/>
+      <c r="DF171" s="24" t="n"/>
+      <c r="DG171" s="24" t="n"/>
+      <c r="DH171" s="24" t="n"/>
+      <c r="DI171" s="24" t="n"/>
+      <c r="DJ171" s="24" t="n"/>
+      <c r="DK171" s="24" t="n"/>
+      <c r="DL171" s="24" t="n"/>
+      <c r="DM171" s="24" t="n"/>
+      <c r="DN171" s="24" t="n"/>
+      <c r="DO171" s="24" t="n"/>
+      <c r="DP171" s="24" t="n"/>
+      <c r="DQ171" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "f828956be898ea82909cc2c95471f23915163bd39f9e25da1a377dad461ebb9b", "away_team": "Lotte Giants", "draw_settlement_value": 0.5, "event_id": "150825", "event_start_utc": "2026-10-12T09:30:00Z", "features": {"away_elo": 1484.286182, "base_tie_rate": 0.02258642, "home_advantage": 20.0, "home_elo": 1519.40969}, "historical_source_observation_times_verified": false, "home_team": "Doosan Bears", "inference_inputs": {"away_id": "LOTTE", "base_tie_rate": 0.02258642, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DOOSAN": 1519.40969, "LOTTE": 1484.286182}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "DOOSAN", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-12T05:39:16.914450+00:00", "outcome_probabilities": {"away": 0.4118135618586591, "draw": 0.02258642, "home": 0.5656000181413409}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.423107, "home": 0.576893}, "snapshot_hash": "a3c933a5546196d889ef02b4634a48b6cafaa117eb9a807e14f0674e3fa214b1", "sport": "KBO"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="36" customHeight="1">
+      <c r="A172" s="24" t="inlineStr">
+        <is>
+          <t>613e1001692c4438</t>
+        </is>
+      </c>
+      <c r="B172" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T05:39:17.217038Z</t>
+        </is>
+      </c>
+      <c r="C172" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D172" s="24" t="inlineStr">
+        <is>
+          <t>150826</t>
+        </is>
+      </c>
+      <c r="E172" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F172" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="G172" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="H172" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I172" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J172" s="25" t="n"/>
+      <c r="K172" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L172" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="M172" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="N172" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="O172" s="28" t="n">
+        <v>0.555504</v>
+      </c>
+      <c r="P172" s="28" t="n"/>
+      <c r="Q172" s="28" t="n">
+        <v>0.0457</v>
+      </c>
+      <c r="R172" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="S172" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T172" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U172" s="24" t="inlineStr">
+        <is>
+          <t>settled</t>
+        </is>
+      </c>
+      <c r="V172" s="24" t="inlineStr">
+        <is>
+          <t>win</t>
+        </is>
+      </c>
+      <c r="W172" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="X172" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y172" s="25" t="n"/>
+      <c r="Z172" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="AA172" s="28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AB172" s="28" t="n">
+        <v>0.000196</v>
+      </c>
+      <c r="AC172" s="30" t="n">
+        <v>0.9615</v>
+      </c>
+      <c r="AD172" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T16:15:09.308348Z</t>
+        </is>
+      </c>
+      <c r="AE172" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.5100 (market_slug=aec-kbo-kti-ltg-2026-10-12). Tie probability=0.0226.</t>
+        </is>
+      </c>
+      <c r="AF172" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG172" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH172" s="24" t="n"/>
+      <c r="AI172" s="31" t="n"/>
+      <c r="AJ172" s="31" t="n"/>
+      <c r="AK172" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL172" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM172" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN172" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO172" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP172" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AQ172" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AR172" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AS172" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AT172" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AU172" s="24" t="inlineStr">
+        <is>
+          <t>Kia Tigers</t>
+        </is>
+      </c>
+      <c r="AV172" s="24" t="n"/>
+      <c r="AW172" s="24" t="n"/>
+      <c r="AX172" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY172" s="24" t="n"/>
+      <c r="AZ172" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA172" s="24" t="inlineStr">
+        <is>
+          <t>f828956be898ea82909cc2c95471f23915163bd39f9e25da1a377dad461ebb9b</t>
+        </is>
+      </c>
+      <c r="BB172" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC172" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD172" s="24" t="inlineStr">
+        <is>
+          <t>f828956be898ea82909cc2c95471f23915163bd39f9e25da1a377dad461ebb9b</t>
+        </is>
+      </c>
+      <c r="BE172" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF172" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG172" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH172" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-12T05:39:17.217038Z</t>
+        </is>
+      </c>
+      <c r="BI172" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ172" s="25" t="n"/>
+      <c r="BK172" s="26" t="n">
+        <v>-104</v>
+      </c>
+      <c r="BL172" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BM172" s="28" t="n">
+        <v>0.509804</v>
+      </c>
+      <c r="BN172" s="28" t="n"/>
+      <c r="BO172" s="28" t="n"/>
+      <c r="BP172" s="25" t="n"/>
+      <c r="BQ172" s="27" t="n">
+        <v>1.961538</v>
+      </c>
+      <c r="BR172" s="28" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="BS172" s="28" t="n"/>
+      <c r="BT172" s="28" t="n"/>
+      <c r="BU172" s="25" t="n"/>
+      <c r="BV172" s="29" t="n"/>
+      <c r="BW172" s="24" t="n"/>
+      <c r="BX172" s="30" t="n"/>
+      <c r="BY172" s="27" t="n"/>
+      <c r="BZ172" s="24" t="n"/>
+      <c r="CA172" s="31" t="n"/>
+      <c r="CB172" s="24" t="n"/>
+      <c r="CC172" s="24" t="n"/>
+      <c r="CD172" s="24" t="n"/>
+      <c r="CE172" s="24" t="n"/>
+      <c r="CF172" s="24" t="n"/>
+      <c r="CG172" s="24" t="n"/>
+      <c r="CH172" s="24" t="n"/>
+      <c r="CI172" s="24" t="n"/>
+      <c r="CJ172" s="24" t="n"/>
+      <c r="CK172" s="24" t="n"/>
+      <c r="CL172" s="24" t="n"/>
+      <c r="CM172" s="24" t="n"/>
+      <c r="CN172" s="24" t="n"/>
+      <c r="CO172" s="24" t="n"/>
+      <c r="CP172" s="24" t="n"/>
+      <c r="CQ172" s="24" t="n"/>
+      <c r="CR172" s="24" t="n"/>
+      <c r="CS172" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT172" s="24" t="n"/>
+      <c r="CU172" s="24" t="n"/>
+      <c r="CV172" s="24" t="n"/>
+      <c r="CW172" s="24" t="n"/>
+      <c r="CX172" s="24" t="n"/>
+      <c r="CY172" s="24" t="n"/>
+      <c r="CZ172" s="24" t="n"/>
+      <c r="DA172" s="24" t="n"/>
+      <c r="DB172" s="24" t="n"/>
+      <c r="DC172" s="24" t="n"/>
+      <c r="DD172" s="24" t="n"/>
+      <c r="DE172" s="24" t="n"/>
+      <c r="DF172" s="24" t="n"/>
+      <c r="DG172" s="24" t="n"/>
+      <c r="DH172" s="24" t="n"/>
+      <c r="DI172" s="24" t="n"/>
+      <c r="DJ172" s="24" t="n"/>
+      <c r="DK172" s="24" t="n"/>
+      <c r="DL172" s="24" t="n"/>
+      <c r="DM172" s="24" t="n"/>
+      <c r="DN172" s="24" t="n"/>
+      <c r="DO172" s="24" t="n"/>
+      <c r="DP172" s="24" t="n"/>
+      <c r="DQ172" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "f828956be898ea82909cc2c95471f23915163bd39f9e25da1a377dad461ebb9b", "away_team": "LG Twins", "draw_settlement_value": 0.5, "event_id": "150826", "event_start_utc": "2026-10-12T09:30:00Z", "features": {"away_elo": 1510.493341, "base_tie_rate": 0.02258642, "home_advantage": 20.0, "home_elo": 1530.123769}, "historical_source_observation_times_verified": false, "home_team": "Kia Tigers", "inference_inputs": {"away_id": "LG", "base_tie_rate": 0.02258642, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"KIA": 1530.123769, "LG": 1510.493341}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "KIA", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-12T05:39:16.914450+00:00", "outcome_probabilities": {"away": 0.433202697383019, "draw": 0.02258642, "home": 0.544210882616981}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.444496, "home": 0.555504}, "snapshot_hash": "1abf9f56510029fa32df9cc61fe09feb73cb594b4d6317de7c8a57cac5a0dd14", "sport": "KBO"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="36" customHeight="1">
+      <c r="A173" s="24" t="inlineStr">
+        <is>
+          <t>f8d26603db2e4cbd</t>
+        </is>
+      </c>
+      <c r="B173" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:28:51.817150Z</t>
+        </is>
+      </c>
+      <c r="C173" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-14T09:30:00Z</t>
+        </is>
+      </c>
+      <c r="D173" s="24" t="inlineStr">
+        <is>
+          <t>156781</t>
+        </is>
+      </c>
+      <c r="E173" s="24" t="inlineStr">
+        <is>
+          <t>KBO</t>
+        </is>
+      </c>
+      <c r="F173" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="G173" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="H173" s="24" t="inlineStr">
+        <is>
+          <t>moneyline</t>
+        </is>
+      </c>
+      <c r="I173" s="24" t="inlineStr">
+        <is>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="J173" s="25" t="n"/>
+      <c r="K173" s="24" t="inlineStr">
+        <is>
+          <t>polymarket_us</t>
+        </is>
+      </c>
+      <c r="L173" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="M173" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N173" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="O173" s="28" t="n">
+        <v>0.517455</v>
+      </c>
+      <c r="P173" s="28" t="n"/>
+      <c r="Q173" s="28" t="n">
+        <v>0.047971</v>
+      </c>
+      <c r="R173" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="S173" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="T173" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="U173" s="24" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="V173" s="24" t="n"/>
+      <c r="W173" s="26" t="n"/>
+      <c r="X173" s="26" t="n"/>
+      <c r="Y173" s="25" t="n"/>
+      <c r="Z173" s="26" t="n"/>
+      <c r="AA173" s="28" t="n"/>
+      <c r="AB173" s="28" t="n"/>
+      <c r="AC173" s="30" t="n"/>
+      <c r="AD173" s="24" t="n"/>
+      <c r="AE173" s="31" t="inlineStr">
+        <is>
+          <t>Tie-aware Elo baseline; executable ask 0.4700 (market_slug=aec-kbo-ltg-dbo-2026-10-14). Tie probability=0.0226.</t>
+        </is>
+      </c>
+      <c r="AF173" s="31" t="inlineStr">
+        <is>
+          <t>Config-promoted international baseball baseline; gates enforced at log time.</t>
+        </is>
+      </c>
+      <c r="AG173" s="24" t="inlineStr">
+        <is>
+          <t>not_applicable</t>
+        </is>
+      </c>
+      <c r="AH173" s="24" t="n"/>
+      <c r="AI173" s="31" t="n"/>
+      <c r="AJ173" s="31" t="n"/>
+      <c r="AK173" s="24" t="inlineStr">
+        <is>
+          <t>paper_call</t>
+        </is>
+      </c>
+      <c r="AL173" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AM173" s="24" t="inlineStr">
+        <is>
+          <t>RESEARCH_OBSERVATION</t>
+        </is>
+      </c>
+      <c r="AN173" s="24" t="inlineStr">
+        <is>
+          <t>CALL</t>
+        </is>
+      </c>
+      <c r="AO173" s="24" t="inlineStr">
+        <is>
+          <t>PAPER_CALL_LOW_EDGE</t>
+        </is>
+      </c>
+      <c r="AP173" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AQ173" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AR173" s="24" t="inlineStr">
+        <is>
+          <t>Doosan Bears</t>
+        </is>
+      </c>
+      <c r="AS173" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AT173" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AU173" s="24" t="inlineStr">
+        <is>
+          <t>LG Twins</t>
+        </is>
+      </c>
+      <c r="AV173" s="24" t="n"/>
+      <c r="AW173" s="24" t="n"/>
+      <c r="AX173" s="24" t="inlineStr">
+        <is>
+          <t>statistical_model</t>
+        </is>
+      </c>
+      <c r="AY173" s="24" t="n"/>
+      <c r="AZ173" s="24" t="inlineStr">
+        <is>
+          <t>shadow_qualified</t>
+        </is>
+      </c>
+      <c r="BA173" s="24" t="inlineStr">
+        <is>
+          <t>a8edff19ea33759e916156f0340eeb6b44b7dd1ede0ca462f6ded28493f70ba6</t>
+        </is>
+      </c>
+      <c r="BB173" s="24" t="inlineStr">
+        <is>
+          <t>tie_aware_elo</t>
+        </is>
+      </c>
+      <c r="BC173" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BD173" s="24" t="inlineStr">
+        <is>
+          <t>a8edff19ea33759e916156f0340eeb6b44b7dd1ede0ca462f6ded28493f70ba6</t>
+        </is>
+      </c>
+      <c r="BE173" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BF173" s="24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BG173" s="24" t="inlineStr">
+        <is>
+          <t>kbo-tie-aware-elo-v2</t>
+        </is>
+      </c>
+      <c r="BH173" s="24" t="inlineStr">
+        <is>
+          <t>2026-10-13T22:28:51.817150Z</t>
+        </is>
+      </c>
+      <c r="BI173" s="24" t="inlineStr">
+        <is>
+          <t>["same_event","same_team_same_day","same_league_same_day"]</t>
+        </is>
+      </c>
+      <c r="BJ173" s="25" t="n"/>
+      <c r="BK173" s="26" t="n">
+        <v>113</v>
+      </c>
+      <c r="BL173" s="27" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="BM173" s="28" t="n">
+        <v>0.469484</v>
+      </c>
+      <c r="BN173" s="28" t="n"/>
+      <c r="BO173" s="28" t="n"/>
+      <c r="BP173" s="25" t="n"/>
+      <c r="BQ173" s="27" t="n"/>
+      <c r="BR173" s="28" t="n"/>
+      <c r="BS173" s="28" t="n"/>
+      <c r="BT173" s="28" t="n"/>
+      <c r="BU173" s="25" t="n"/>
+      <c r="BV173" s="29" t="n"/>
+      <c r="BW173" s="24" t="n"/>
+      <c r="BX173" s="30" t="n"/>
+      <c r="BY173" s="27" t="n"/>
+      <c r="BZ173" s="24" t="n"/>
+      <c r="CA173" s="31" t="n"/>
+      <c r="CB173" s="24" t="n"/>
+      <c r="CC173" s="24" t="n"/>
+      <c r="CD173" s="24" t="n"/>
+      <c r="CE173" s="24" t="n"/>
+      <c r="CF173" s="24" t="n"/>
+      <c r="CG173" s="24" t="n"/>
+      <c r="CH173" s="24" t="n"/>
+      <c r="CI173" s="24" t="n"/>
+      <c r="CJ173" s="24" t="n"/>
+      <c r="CK173" s="24" t="n"/>
+      <c r="CL173" s="24" t="n"/>
+      <c r="CM173" s="24" t="n"/>
+      <c r="CN173" s="24" t="n"/>
+      <c r="CO173" s="24" t="n"/>
+      <c r="CP173" s="24" t="n"/>
+      <c r="CQ173" s="24" t="n"/>
+      <c r="CR173" s="24" t="n"/>
+      <c r="CS173" s="24" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="CT173" s="24" t="n"/>
+      <c r="CU173" s="24" t="n"/>
+      <c r="CV173" s="24" t="n"/>
+      <c r="CW173" s="24" t="n"/>
+      <c r="CX173" s="24" t="n"/>
+      <c r="CY173" s="24" t="n"/>
+      <c r="CZ173" s="24" t="n"/>
+      <c r="DA173" s="24" t="n"/>
+      <c r="DB173" s="24" t="n"/>
+      <c r="DC173" s="24" t="n"/>
+      <c r="DD173" s="24" t="n"/>
+      <c r="DE173" s="24" t="n"/>
+      <c r="DF173" s="24" t="n"/>
+      <c r="DG173" s="24" t="n"/>
+      <c r="DH173" s="24" t="n"/>
+      <c r="DI173" s="24" t="n"/>
+      <c r="DJ173" s="24" t="n"/>
+      <c r="DK173" s="24" t="n"/>
+      <c r="DL173" s="24" t="n"/>
+      <c r="DM173" s="24" t="n"/>
+      <c r="DN173" s="24" t="n"/>
+      <c r="DO173" s="24" t="n"/>
+      <c r="DP173" s="24" t="n"/>
+      <c r="DQ173" s="24" t="inlineStr">
+        <is>
+          <t>{"artifact_hash": "a8edff19ea33759e916156f0340eeb6b44b7dd1ede0ca462f6ded28493f70ba6", "away_team": "Doosan Bears", "draw_settlement_value": 0.5, "event_id": "156781", "event_start_utc": "2026-10-14T09:30:00Z", "features": {"away_elo": 1514.491213, "base_tie_rate": 0.02257709, "home_advantage": 20.0, "home_elo": 1506.905724}, "historical_source_observation_times_verified": false, "home_team": "LG Twins", "inference_inputs": {"away_id": "DOOSAN", "base_tie_rate": 0.02257709, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DOOSAN": 1514.491213, "LG": 1506.905724}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "LG", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-13T22:28:51.165973+00:00", "outcome_probabilities": {"away": 0.4712563260098324, "draw": 0.02257709, "home": 0.5061665839901677}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.482545, "home": 0.517455}, "snapshot_hash": "f882f37433c0065bdadd8cf508c7d60dfe772b18ee84ebf7e3a79569e5493f65", "sport": "KBO"}</t>
         </is>
       </c>
     </row>

--- a/data/sports/kbo/research.xlsx
+++ b/data/sports/kbo/research.xlsx
@@ -55603,12 +55603,12 @@
     <row r="173" ht="36" customHeight="1">
       <c r="A173" s="24" t="inlineStr">
         <is>
-          <t>f8d26603db2e4cbd</t>
+          <t>4c517d8b5c8f4c9a</t>
         </is>
       </c>
       <c r="B173" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:28:51.817150Z</t>
+          <t>2026-10-14T05:52:00.939109Z</t>
         </is>
       </c>
       <c r="C173" s="24" t="inlineStr">
@@ -55653,26 +55653,26 @@
         </is>
       </c>
       <c r="L173" s="26" t="n">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="M173" s="27" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="N173" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.4</v>
       </c>
       <c r="O173" s="28" t="n">
         <v>0.517455</v>
       </c>
       <c r="P173" s="28" t="n"/>
       <c r="Q173" s="28" t="n">
-        <v>0.047971</v>
+        <v>0.117455</v>
       </c>
       <c r="R173" s="26" t="n">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="S173" s="29" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="T173" s="24" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
       <c r="AD173" s="24" t="n"/>
       <c r="AE173" s="31" t="inlineStr">
         <is>
-          <t>Tie-aware Elo baseline; executable ask 0.4700 (market_slug=aec-kbo-ltg-dbo-2026-10-14). Tie probability=0.0226.</t>
+          <t>Tie-aware Elo baseline; executable ask 0.4000 (market_slug=aec-kbo-ltg-dbo-2026-10-14). Tie probability=0.0226.</t>
         </is>
       </c>
       <c r="AF173" s="31" t="inlineStr">
@@ -55779,7 +55779,7 @@
       </c>
       <c r="BA173" s="24" t="inlineStr">
         <is>
-          <t>a8edff19ea33759e916156f0340eeb6b44b7dd1ede0ca462f6ded28493f70ba6</t>
+          <t>4df516736af526c49ca03fe912f4ebe7438a5556f6b821ff0d158dc7c26c3f65</t>
         </is>
       </c>
       <c r="BB173" s="24" t="inlineStr">
@@ -55794,7 +55794,7 @@
       </c>
       <c r="BD173" s="24" t="inlineStr">
         <is>
-          <t>a8edff19ea33759e916156f0340eeb6b44b7dd1ede0ca462f6ded28493f70ba6</t>
+          <t>4df516736af526c49ca03fe912f4ebe7438a5556f6b821ff0d158dc7c26c3f65</t>
         </is>
       </c>
       <c r="BE173" s="24" t="inlineStr">
@@ -55814,7 +55814,7 @@
       </c>
       <c r="BH173" s="24" t="inlineStr">
         <is>
-          <t>2026-10-13T22:28:51.817150Z</t>
+          <t>2026-10-14T05:52:00.938495Z</t>
         </is>
       </c>
       <c r="BI173" s="24" t="inlineStr">
@@ -55824,13 +55824,13 @@
       </c>
       <c r="BJ173" s="25" t="n"/>
       <c r="BK173" s="26" t="n">
-        <v>113</v>
+        <v>150</v>
       </c>
       <c r="BL173" s="27" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="BM173" s="28" t="n">
-        <v>0.469484</v>
+        <v>0.4</v>
       </c>
       <c r="BN173" s="28" t="n"/>
       <c r="BO173" s="28" t="n"/>
@@ -55893,7 +55893,7 @@
       <c r="DP173" s="24" t="n"/>
       <c r="DQ173" s="24" t="inlineStr">
         <is>
-          <t>{"artifact_hash": "a8edff19ea33759e916156f0340eeb6b44b7dd1ede0ca462f6ded28493f70ba6", "away_team": "Doosan Bears", "draw_settlement_value": 0.5, "event_id": "156781", "event_start_utc": "2026-10-14T09:30:00Z", "features": {"away_elo": 1514.491213, "base_tie_rate": 0.02257709, "home_advantage": 20.0, "home_elo": 1506.905724}, "historical_source_observation_times_verified": false, "home_team": "LG Twins", "inference_inputs": {"away_id": "DOOSAN", "base_tie_rate": 0.02257709, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DOOSAN": 1514.491213, "LG": 1506.905724}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "fe583791ae4febdb6b477e979042a87e118f547c292d23a5c6651da0218cc4e4"}, "home_id": "LG", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-13T22:28:51.165973+00:00", "outcome_probabilities": {"away": 0.4712563260098324, "draw": 0.02257709, "home": 0.5061665839901677}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.482545, "home": 0.517455}, "snapshot_hash": "f882f37433c0065bdadd8cf508c7d60dfe772b18ee84ebf7e3a79569e5493f65", "sport": "KBO"}</t>
+          <t>{"artifact_hash": "4df516736af526c49ca03fe912f4ebe7438a5556f6b821ff0d158dc7c26c3f65", "away_team": "Doosan Bears", "draw_settlement_value": 0.5, "event_id": "156781", "event_start_utc": "2026-10-14T09:30:00Z", "features": {"away_elo": 1514.491213, "base_tie_rate": 0.02257709, "home_advantage": 20.0, "home_elo": 1506.905724}, "historical_source_observation_times_verified": false, "home_team": "LG Twins", "inference_inputs": {"away_id": "DOOSAN", "base_tie_rate": 0.02257709, "book_state": {"_games_played": null, "_last_active": null, "decay_rate": 0.001, "home_advantage": 20.0, "k": 8.0, "margin_weight": 0.0, "ratings": {"DOOSAN": 1514.491213, "LG": 1506.905724}}, "code_sha256": {"features/elo_ratings.py": "d6513e79d65448c06cc0f9b9eed0eaa091567835128e1f6647a310da8d78a872", "international_baseball.py": "8d592e32eff91d945b870d7032edca3806863cff9428edece9f38d56cc36b070"}, "home_id": "LG", "tie_method": "flat"}, "market_type": "moneyline", "model_version": "kbo-tie-aware-elo-v2", "observed_at_utc": "2026-10-14T05:52:00.225750+00:00", "outcome_probabilities": {"away": 0.4712563260098324, "draw": 0.02257709, "home": 0.5061665839901677}, "replay_scope": "Exact Elo and tie model; logged value is expected contract settlement, not outright win probability.", "schema": "international-elo-replay-v1", "settlement_values": {"away": 0.482545, "home": 0.517455}, "snapshot_hash": "a09919bb5119957c4725b1513051ef3bb8335141c1ba893a6ff8a22530e0ce3b", "sport": "KBO"}</t>
         </is>
       </c>
     </row>
